--- a/db/data/BMS-MassUpload-Complete.xlsx
+++ b/db/data/BMS-MassUpload-Complete.xlsx
@@ -50,9 +50,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -1803,650 +1802,668 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1001</v>
+      <c r="A2" t="str">
+        <v/>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
         <v>BRG-NSW-SYD-001</v>
       </c>
-      <c r="D2" t="str">
-        <v>Sydney Harbour Bridge</v>
-      </c>
       <c r="E2" t="str">
+        <v>Harbour Gate Bridge</v>
+      </c>
+      <c r="F2" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F2" t="str">
-        <v>Cahill Expressway</v>
-      </c>
       <c r="G2" t="str">
+        <v>Harbour City Expressway</v>
+      </c>
+      <c r="H2" t="str">
         <v>A8</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>NSW</v>
       </c>
-      <c r="I2" t="str">
-        <v>Sydney Metro</v>
-      </c>
       <c r="J2" t="str">
-        <v>North Sydney</v>
+        <v>Sydney Metropolitan</v>
       </c>
       <c r="K2" t="str">
-        <v>-33.852306</v>
-      </c>
-      <c r="L2" t="str">
-        <v>151.210787</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Sydney Harbour</v>
+        <v>North Haven</v>
+      </c>
+      <c r="L2">
+        <v>-33.7912</v>
+      </c>
+      <c r="M2">
+        <v>151.2524</v>
       </c>
       <c r="N2" t="str">
-        <v>Transport for NSW</v>
+        <v>Kestrel Harbour</v>
       </c>
       <c r="O2" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="P2" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q2" t="str">
         <v>Arch Bridge</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>1932</v>
       </c>
-      <c r="R2" t="str">
+      <c r="S2" t="str">
         <v>T44</v>
       </c>
-      <c r="S2" t="str">
+      <c r="T2" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T2" t="str">
-        <v>49.00</v>
-      </c>
-      <c r="U2" t="str">
-        <v>503.00</v>
-      </c>
-      <c r="V2" t="str">
+      <c r="U2">
+        <v>49</v>
+      </c>
+      <c r="V2">
+        <v>503</v>
+      </c>
+      <c r="W2" t="str">
         <v>Steel</v>
       </c>
-      <c r="W2">
-        <v>1</v>
-      </c>
-      <c r="X2" t="str">
-        <v>1149.00</v>
-      </c>
-      <c r="Y2" t="str">
-        <v>48.80</v>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1149</v>
       </c>
       <c r="Z2">
+        <v>48.8</v>
+      </c>
+      <c r="AA2">
         <v>8</v>
       </c>
-      <c r="AA2" t="str">
-        <v>Good</v>
-      </c>
-      <c r="AB2">
+      <c r="AB2" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC2">
+        <v>2</v>
+      </c>
+      <c r="AD2">
+        <v>9</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>Unrestricted</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>AS 5100.7</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>Zone 1</v>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="str">
+        <v>Landmark steel arch bridge. Major strategic crossing with ongoing structural monitoring program.</v>
+      </c>
+      <c r="AM2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN2" t="str">
+        <v>2025-11-14</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="AQ2">
+        <v>42.5</v>
+      </c>
+      <c r="AR2" t="str">
+        <v/>
+      </c>
+      <c r="AS2" t="str">
+        <v/>
+      </c>
+      <c r="AT2">
+        <v>160000</v>
+      </c>
+      <c r="AU2">
+        <v>18.5</v>
+      </c>
+      <c r="AV2" t="str">
+        <v/>
+      </c>
+      <c r="AW2" t="str">
+        <v/>
+      </c>
+      <c r="AX2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="str">
+        <v>DEMO</v>
+      </c>
+      <c r="BC2" t="str">
+        <v/>
+      </c>
+      <c r="BD2" t="str">
+        <v/>
+      </c>
+      <c r="BE2" t="str">
+        <v/>
+      </c>
+      <c r="BF2" t="str">
+        <v/>
+      </c>
+      <c r="BG2" t="str">
+        <v>{"type":"LineString","coordinates":[[151.248,-33.791],[151.252,-33.791]]}</v>
+      </c>
+      <c r="BH2" t="str">
+        <v/>
+      </c>
+      <c r="BI2" t="str">
+        <v/>
+      </c>
+      <c r="BJ2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>BRG-NSW-SYD-002</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Blackwattle Crossing</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Road Bridge</v>
+      </c>
+      <c r="G3" t="str">
+        <v>City West Link</v>
+      </c>
+      <c r="H3" t="str">
+        <v>M4</v>
+      </c>
+      <c r="I3" t="str">
+        <v>NSW</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Sydney Metropolitan</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Harborside</v>
+      </c>
+      <c r="L3">
+        <v>-33.8415</v>
+      </c>
+      <c r="M3">
+        <v>151.1489</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Kestrel Bay</v>
+      </c>
+      <c r="O3" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P3" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Cable-stayed Bridge</v>
+      </c>
+      <c r="R3">
+        <v>1995</v>
+      </c>
+      <c r="S3" t="str">
+        <v>SM1600</v>
+      </c>
+      <c r="T3" t="str">
+        <v>AS5100</v>
+      </c>
+      <c r="U3">
+        <v>40</v>
+      </c>
+      <c r="V3">
+        <v>345</v>
+      </c>
+      <c r="W3" t="str">
+        <v>Concrete and Steel</v>
+      </c>
+      <c r="X3">
+        <v>3</v>
+      </c>
+      <c r="Y3">
+        <v>805</v>
+      </c>
+      <c r="Z3">
+        <v>32.2</v>
+      </c>
+      <c r="AA3">
+        <v>6</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC3">
+        <v>2</v>
+      </c>
+      <c r="AD3">
         <v>8</v>
       </c>
-      <c r="AC2">
+      <c r="AE3" t="str">
+        <v>Unrestricted</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>AS 5100</v>
+      </c>
+      <c r="AG3" t="str">
+        <v>Zone 1</v>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="str">
+        <v>Major cable-stayed bridge linking inner-city precincts. Urban freight corridor.</v>
+      </c>
+      <c r="AM3" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN3" t="str">
+        <v>2025-10-02</v>
+      </c>
+      <c r="AO3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="str">
+        <v>2025-10-08</v>
+      </c>
+      <c r="AQ3">
+        <v>36.5</v>
+      </c>
+      <c r="AR3" t="str">
+        <v/>
+      </c>
+      <c r="AS3" t="str">
+        <v/>
+      </c>
+      <c r="AT3">
+        <v>95000</v>
+      </c>
+      <c r="AU3">
+        <v>16.25</v>
+      </c>
+      <c r="AV3" t="str">
+        <v/>
+      </c>
+      <c r="AW3" t="str">
+        <v/>
+      </c>
+      <c r="AX3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA3" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="str">
+        <v>DEMO</v>
+      </c>
+      <c r="BC3" t="str">
+        <v/>
+      </c>
+      <c r="BD3" t="str">
+        <v/>
+      </c>
+      <c r="BE3" t="str">
+        <v/>
+      </c>
+      <c r="BF3" t="str">
+        <v/>
+      </c>
+      <c r="BG3" t="str">
+        <v>{"type":"LineString","coordinates":[[151.153,-33.841],[151.149,-33.841]]}</v>
+      </c>
+      <c r="BH3" t="str">
+        <v/>
+      </c>
+      <c r="BI3" t="str">
+        <v/>
+      </c>
+      <c r="BJ3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>BRG-NSW-SYD-003</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Riverview Arch Bridge</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Road Bridge</v>
+      </c>
+      <c r="G4" t="str">
+        <v>River Road</v>
+      </c>
+      <c r="H4" t="str">
+        <v>A40</v>
+      </c>
+      <c r="I4" t="str">
+        <v>NSW</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Sydney Metropolitan</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Riverton</v>
+      </c>
+      <c r="L4">
+        <v>-33.8043</v>
+      </c>
+      <c r="M4">
+        <v>151.0982</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Greywood River</v>
+      </c>
+      <c r="O4" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P4" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Arch Bridge</v>
+      </c>
+      <c r="R4">
+        <v>1964</v>
+      </c>
+      <c r="S4" t="str">
+        <v>T44</v>
+      </c>
+      <c r="T4" t="str">
+        <v>AS5100</v>
+      </c>
+      <c r="U4">
+        <v>29.3</v>
+      </c>
+      <c r="V4">
+        <v>305</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Concrete</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>579</v>
+      </c>
+      <c r="Z4">
+        <v>22.8</v>
+      </c>
+      <c r="AA4">
+        <v>4</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC4">
+        <v>3</v>
+      </c>
+      <c r="AD4">
+        <v>7</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>Unrestricted</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>AS 5100.7</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>Zone 1</v>
+      </c>
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4" t="str">
+        <v/>
+      </c>
+      <c r="AJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>Long-span concrete arch. Approaching end of design life — major inspection 2026.</v>
+      </c>
+      <c r="AM4" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN4" t="str">
+        <v>2025-08-19</v>
+      </c>
+      <c r="AO4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="AQ4">
+        <v>32</v>
+      </c>
+      <c r="AR4" t="str">
+        <v/>
+      </c>
+      <c r="AS4" t="str">
+        <v/>
+      </c>
+      <c r="AT4">
+        <v>72000</v>
+      </c>
+      <c r="AU4">
         <v>9</v>
       </c>
-      <c r="AD2" t="str">
-        <v>Unrestricted</v>
-      </c>
-      <c r="AE2" t="str">
+      <c r="AV4" t="str">
+        <v/>
+      </c>
+      <c r="AW4" t="str">
+        <v/>
+      </c>
+      <c r="AX4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB4" t="str">
+        <v>DEMO</v>
+      </c>
+      <c r="BC4" t="str">
+        <v/>
+      </c>
+      <c r="BD4" t="str">
+        <v/>
+      </c>
+      <c r="BE4" t="str">
+        <v/>
+      </c>
+      <c r="BF4" t="str">
+        <v/>
+      </c>
+      <c r="BG4" t="str">
+        <v>{"type":"LineString","coordinates":[[151.094,-33.804],[151.099,-33.804]]}</v>
+      </c>
+      <c r="BH4" t="str">
+        <v/>
+      </c>
+      <c r="BI4" t="str">
+        <v/>
+      </c>
+      <c r="BJ4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>BRG-NSW-SYD-004</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Coxley Cove Bridge</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Road Bridge</v>
+      </c>
+      <c r="G5" t="str">
+        <v>River Road</v>
+      </c>
+      <c r="H5" t="str">
+        <v>A40</v>
+      </c>
+      <c r="I5" t="str">
+        <v>NSW</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Sydney Metropolitan</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Westbay</v>
+      </c>
+      <c r="L5">
+        <v>-33.8826</v>
+      </c>
+      <c r="M5">
+        <v>151.1183</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Coxley Cove</v>
+      </c>
+      <c r="O5" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P5" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>Girder Bridge</v>
+      </c>
+      <c r="R5">
+        <v>1953</v>
+      </c>
+      <c r="S5" t="str">
+        <v>T44</v>
+      </c>
+      <c r="T5" t="str">
+        <v>AS5100</v>
+      </c>
+      <c r="U5">
+        <v>12</v>
+      </c>
+      <c r="V5">
+        <v>64</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Steel</v>
+      </c>
+      <c r="X5">
+        <v>5</v>
+      </c>
+      <c r="Y5">
+        <v>340</v>
+      </c>
+      <c r="Z5">
+        <v>18.6</v>
+      </c>
+      <c r="AA5">
+        <v>4</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC5">
+        <v>3</v>
+      </c>
+      <c r="AD5">
+        <v>5</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>Restricted</v>
+      </c>
+      <c r="AF5" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF2" t="str">
+      <c r="AG5" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG2" t="str">
-        <v/>
-      </c>
-      <c r="AH2" t="str">
-        <v/>
-      </c>
-      <c r="AI2" t="str">
-        <v/>
-      </c>
-      <c r="AJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="str">
-        <v>Iconic steel arch bridge. Major strategic crossing with ongoing structural monitoring program.</v>
-      </c>
-      <c r="AM2" t="str">
-        <v>Inactive</v>
-      </c>
-      <c r="AN2" t="str">
-        <v>Low</v>
-      </c>
-      <c r="AO2" t="str">
-        <v>2025-11-14</v>
-      </c>
-      <c r="AP2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ2" t="str">
-        <v>2025-11-20</v>
-      </c>
-      <c r="AR2" t="str">
-        <v>42.50</v>
-      </c>
-      <c r="AS2" t="str">
-        <v/>
-      </c>
-      <c r="AT2" t="str">
-        <v/>
-      </c>
-      <c r="AU2">
-        <v>160000</v>
-      </c>
-      <c r="AV2" t="str">
-        <v>18.50</v>
-      </c>
-      <c r="AW2" t="str">
-        <v/>
-      </c>
-      <c r="AX2" t="str">
-        <v/>
-      </c>
-      <c r="AY2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC2" t="str">
-        <v>DEMO</v>
-      </c>
-      <c r="BD2" t="str">
-        <v/>
-      </c>
-      <c r="BE2" t="str">
-        <v/>
-      </c>
-      <c r="BF2" t="str">
-        <v/>
-      </c>
-      <c r="BG2" t="str">
-        <v/>
-      </c>
-      <c r="BH2" t="str">
-        <v>{"type":"LineString","coordinates":[[151.206,-33.852],[151.210,-33.852]]}</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>1002</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v>BRG-NSW-SYD-002</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Anzac Bridge</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Road Bridge</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Western Distributor</v>
-      </c>
-      <c r="G3" t="str">
-        <v>M4</v>
-      </c>
-      <c r="H3" t="str">
-        <v>NSW</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Sydney Metro</v>
-      </c>
-      <c r="J3" t="str">
-        <v>City of Sydney</v>
-      </c>
-      <c r="K3" t="str">
-        <v>-33.869661</v>
-      </c>
-      <c r="L3" t="str">
-        <v>151.183452</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Johnstons Bay</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Cable-stayed Bridge</v>
-      </c>
-      <c r="Q3">
-        <v>1995</v>
-      </c>
-      <c r="R3" t="str">
-        <v>SM1600</v>
-      </c>
-      <c r="S3" t="str">
-        <v>AS5100</v>
-      </c>
-      <c r="T3" t="str">
-        <v>40.00</v>
-      </c>
-      <c r="U3" t="str">
-        <v>345.00</v>
-      </c>
-      <c r="V3" t="str">
-        <v>Concrete and Steel</v>
-      </c>
-      <c r="W3">
-        <v>3</v>
-      </c>
-      <c r="X3" t="str">
-        <v>805.00</v>
-      </c>
-      <c r="Y3" t="str">
-        <v>32.20</v>
-      </c>
-      <c r="Z3">
-        <v>6</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>Good</v>
-      </c>
-      <c r="AB3">
-        <v>7</v>
-      </c>
-      <c r="AC3">
-        <v>8</v>
-      </c>
-      <c r="AD3" t="str">
-        <v>Unrestricted</v>
-      </c>
-      <c r="AE3" t="str">
-        <v>AS 5100</v>
-      </c>
-      <c r="AF3" t="str">
-        <v>Zone 1</v>
-      </c>
-      <c r="AG3" t="str">
-        <v/>
-      </c>
-      <c r="AH3" t="str">
-        <v/>
-      </c>
-      <c r="AI3" t="str">
-        <v/>
-      </c>
-      <c r="AJ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="str">
-        <v>Major cable-stayed bridge linking Pyrmont and Rozelle. Urban freight corridor.</v>
-      </c>
-      <c r="AM3" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN3" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO3" t="str">
-        <v>2025-10-02</v>
-      </c>
-      <c r="AP3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ3" t="str">
-        <v>2025-10-08</v>
-      </c>
-      <c r="AR3" t="str">
-        <v>36.50</v>
-      </c>
-      <c r="AS3" t="str">
-        <v/>
-      </c>
-      <c r="AT3" t="str">
-        <v/>
-      </c>
-      <c r="AU3">
-        <v>95000</v>
-      </c>
-      <c r="AV3" t="str">
-        <v>16.25</v>
-      </c>
-      <c r="AW3" t="str">
-        <v/>
-      </c>
-      <c r="AX3" t="str">
-        <v/>
-      </c>
-      <c r="AY3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB3" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC3" t="str">
-        <v>DEMO</v>
-      </c>
-      <c r="BD3" t="str">
-        <v/>
-      </c>
-      <c r="BE3" t="str">
-        <v/>
-      </c>
-      <c r="BF3" t="str">
-        <v/>
-      </c>
-      <c r="BG3" t="str">
-        <v/>
-      </c>
-      <c r="BH3" t="str">
-        <v>{"type":"LineString","coordinates":[[151.188,-33.869],[151.183,-33.869]]}</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>1003</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v>BRG-NSW-SYD-003</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Gladesville Bridge</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Road Bridge</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Victoria Road</v>
-      </c>
-      <c r="G4" t="str">
-        <v>A40</v>
-      </c>
-      <c r="H4" t="str">
-        <v>NSW</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Sydney Metro</v>
-      </c>
-      <c r="J4" t="str">
-        <v>City of Ryde</v>
-      </c>
-      <c r="K4" t="str">
-        <v>-33.851500</v>
-      </c>
-      <c r="L4" t="str">
-        <v>151.136700</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Parramatta River</v>
-      </c>
-      <c r="N4" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P4" t="str">
-        <v>Arch Bridge</v>
-      </c>
-      <c r="Q4">
-        <v>1964</v>
-      </c>
-      <c r="R4" t="str">
-        <v>T44</v>
-      </c>
-      <c r="S4" t="str">
-        <v>AS5100</v>
-      </c>
-      <c r="T4" t="str">
-        <v>29.30</v>
-      </c>
-      <c r="U4" t="str">
-        <v>305.00</v>
-      </c>
-      <c r="V4" t="str">
-        <v>Concrete</v>
-      </c>
-      <c r="W4">
-        <v>1</v>
-      </c>
-      <c r="X4" t="str">
-        <v>579.00</v>
-      </c>
-      <c r="Y4" t="str">
-        <v>22.80</v>
-      </c>
-      <c r="Z4">
-        <v>4</v>
-      </c>
-      <c r="AA4" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB4">
-        <v>6</v>
-      </c>
-      <c r="AC4">
-        <v>7</v>
-      </c>
-      <c r="AD4" t="str">
-        <v>Unrestricted</v>
-      </c>
-      <c r="AE4" t="str">
-        <v>AS 5100.7</v>
-      </c>
-      <c r="AF4" t="str">
-        <v>Zone 1</v>
-      </c>
-      <c r="AG4" t="str">
-        <v/>
-      </c>
-      <c r="AH4" t="str">
-        <v/>
-      </c>
-      <c r="AI4" t="str">
-        <v/>
-      </c>
-      <c r="AJ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="str">
-        <v>Longest concrete arch bridge in the world at construction. Approaching end of design life — major inspection 2026.</v>
-      </c>
-      <c r="AM4" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN4" t="str">
-        <v>Low</v>
-      </c>
-      <c r="AO4" t="str">
-        <v>2025-08-19</v>
-      </c>
-      <c r="AP4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="AR4" t="str">
-        <v>32.00</v>
-      </c>
-      <c r="AS4" t="str">
-        <v/>
-      </c>
-      <c r="AT4" t="str">
-        <v/>
-      </c>
-      <c r="AU4">
-        <v>72000</v>
-      </c>
-      <c r="AV4" t="str">
-        <v>9.00</v>
-      </c>
-      <c r="AW4" t="str">
-        <v/>
-      </c>
-      <c r="AX4" t="str">
-        <v/>
-      </c>
-      <c r="AY4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC4" t="str">
-        <v>DEMO</v>
-      </c>
-      <c r="BD4" t="str">
-        <v/>
-      </c>
-      <c r="BE4" t="str">
-        <v/>
-      </c>
-      <c r="BF4" t="str">
-        <v/>
-      </c>
-      <c r="BG4" t="str">
-        <v/>
-      </c>
-      <c r="BH4" t="str">
-        <v>{"type":"LineString","coordinates":[[151.132,-33.851],[151.137,-33.851]]}</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>1004</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v>BRG-NSW-SYD-004</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Iron Cove Bridge</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Road Bridge</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Victoria Road</v>
-      </c>
-      <c r="G5" t="str">
-        <v>A40</v>
-      </c>
-      <c r="H5" t="str">
-        <v>NSW</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Sydney Metro</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Inner West</v>
-      </c>
-      <c r="K5" t="str">
-        <v>-33.858200</v>
-      </c>
-      <c r="L5" t="str">
-        <v>151.155600</v>
-      </c>
-      <c r="M5" t="str">
-        <v>Iron Cove</v>
-      </c>
-      <c r="N5" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O5" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P5" t="str">
-        <v>Girder Bridge</v>
-      </c>
-      <c r="Q5">
-        <v>1953</v>
-      </c>
-      <c r="R5" t="str">
-        <v>T44</v>
-      </c>
-      <c r="S5" t="str">
-        <v>AS5100</v>
-      </c>
-      <c r="T5" t="str">
-        <v>12.00</v>
-      </c>
-      <c r="U5" t="str">
-        <v>64.00</v>
-      </c>
-      <c r="V5" t="str">
-        <v>Steel</v>
-      </c>
-      <c r="W5">
-        <v>5</v>
-      </c>
-      <c r="X5" t="str">
-        <v>340.00</v>
-      </c>
-      <c r="Y5" t="str">
-        <v>18.60</v>
-      </c>
-      <c r="Z5">
-        <v>4</v>
-      </c>
-      <c r="AA5" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB5">
-        <v>5</v>
-      </c>
-      <c r="AC5">
-        <v>5</v>
-      </c>
-      <c r="AD5" t="str">
-        <v>Restricted</v>
-      </c>
-      <c r="AE5" t="str">
-        <v>AS 5100.7</v>
-      </c>
-      <c r="AF5" t="str">
-        <v>Zone 1</v>
-      </c>
-      <c r="AG5" t="str">
-        <v/>
       </c>
       <c r="AH5" t="str">
         <v/>
@@ -2464,40 +2481,40 @@
         <v>Ageing steel girder structure with load restrictions. Replacement feasibility study underway.</v>
       </c>
       <c r="AM5" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN5" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO5" t="str">
         <v>2025-06-12</v>
       </c>
-      <c r="AP5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ5" t="str">
+      <c r="AO5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="str">
         <v>2025-06-20</v>
       </c>
+      <c r="AQ5">
+        <v>28</v>
+      </c>
       <c r="AR5" t="str">
-        <v>28.00</v>
+        <v/>
       </c>
       <c r="AS5" t="str">
         <v/>
       </c>
-      <c r="AT5" t="str">
-        <v/>
+      <c r="AT5">
+        <v>55000</v>
       </c>
       <c r="AU5">
-        <v>55000</v>
+        <v>8.2</v>
       </c>
       <c r="AV5" t="str">
-        <v>8.20</v>
+        <v/>
       </c>
       <c r="AW5" t="str">
         <v/>
       </c>
-      <c r="AX5" t="str">
-        <v/>
+      <c r="AX5" t="b">
+        <v>0</v>
       </c>
       <c r="AY5" t="b">
         <v>0</v>
@@ -2508,309 +2525,321 @@
       <c r="BA5" t="b">
         <v>0</v>
       </c>
-      <c r="BB5" t="b">
-        <v>0</v>
+      <c r="BB5" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC5" t="str">
+        <v/>
+      </c>
+      <c r="BD5" t="str">
+        <v/>
+      </c>
+      <c r="BE5" t="str">
+        <v/>
+      </c>
+      <c r="BF5" t="str">
+        <v/>
+      </c>
+      <c r="BG5" t="str">
+        <v>{"type":"LineString","coordinates":[[151.116,-33.882],[151.121,-33.882]]}</v>
+      </c>
+      <c r="BH5" t="str">
+        <v/>
+      </c>
+      <c r="BI5" t="str">
+        <v/>
+      </c>
+      <c r="BJ5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>BRG-NSW-SYD-005</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Marlow Creek Bridge</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Road Bridge</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Coastal Motorway</v>
+      </c>
+      <c r="H6" t="str">
+        <v>M1</v>
+      </c>
+      <c r="I6" t="str">
+        <v>NSW</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Sydney Metropolitan</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Brackenridge</v>
+      </c>
+      <c r="L6">
+        <v>-33.4568</v>
+      </c>
+      <c r="M6">
+        <v>151.2984</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Marlow Creek</v>
+      </c>
+      <c r="O6" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P6" t="str">
+        <v>Motorway Concession Operator</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Box Girder Bridge</v>
+      </c>
+      <c r="R6">
+        <v>1986</v>
+      </c>
+      <c r="S6" t="str">
+        <v>SM1600</v>
+      </c>
+      <c r="T6" t="str">
+        <v>AS5100</v>
+      </c>
+      <c r="U6">
+        <v>67</v>
+      </c>
+      <c r="V6">
+        <v>240</v>
+      </c>
+      <c r="W6" t="str">
+        <v>Concrete</v>
+      </c>
+      <c r="X6">
+        <v>2</v>
+      </c>
+      <c r="Y6">
+        <v>292</v>
+      </c>
+      <c r="Z6">
+        <v>13.2</v>
+      </c>
+      <c r="AA6">
+        <v>4</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC6">
+        <v>2</v>
+      </c>
+      <c r="AD6">
+        <v>8</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>Unrestricted</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>AS 5100</v>
+      </c>
+      <c r="AG6" t="str">
+        <v>Zone 1</v>
+      </c>
+      <c r="AH6" t="str">
+        <v/>
+      </c>
+      <c r="AI6" t="str">
+        <v/>
+      </c>
+      <c r="AJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="str">
+        <v>High-level box girder crossing at 67 m. Critical freight link on the coastal motorway corridor.</v>
+      </c>
+      <c r="AM6" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN6" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="AO6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="AQ6">
+        <v>40</v>
+      </c>
+      <c r="AR6" t="str">
+        <v/>
+      </c>
+      <c r="AS6" t="str">
+        <v/>
+      </c>
+      <c r="AT6">
+        <v>85000</v>
+      </c>
+      <c r="AU6">
+        <v>22</v>
+      </c>
+      <c r="AV6" t="str">
+        <v/>
+      </c>
+      <c r="AW6" t="str">
+        <v/>
+      </c>
+      <c r="AX6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ6" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB6" t="str">
         <v>DEMO</v>
       </c>
-      <c r="BD5" t="str">
-        <v/>
-      </c>
-      <c r="BE5" t="str">
-        <v/>
-      </c>
-      <c r="BF5" t="str">
-        <v/>
-      </c>
-      <c r="BG5" t="str">
-        <v/>
-      </c>
-      <c r="BH5" t="str">
-        <v>{"type":"LineString","coordinates":[[151.153,-33.858],[151.158,-33.858]]}</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>1005</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v>BRG-NSW-SYD-005</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Mooney Mooney Creek Bridge</v>
-      </c>
-      <c r="E6" t="str">
+      <c r="BC6" t="str">
+        <v/>
+      </c>
+      <c r="BD6" t="str">
+        <v/>
+      </c>
+      <c r="BE6" t="str">
+        <v/>
+      </c>
+      <c r="BF6" t="str">
+        <v/>
+      </c>
+      <c r="BG6" t="str">
+        <v>{"type":"LineString","coordinates":[[151.296,-33.457],[151.301,-33.457]]}</v>
+      </c>
+      <c r="BH6" t="str">
+        <v/>
+      </c>
+      <c r="BI6" t="str">
+        <v/>
+      </c>
+      <c r="BJ6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>BRG-NSW-SYD-006</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Westbrook Bridge</v>
+      </c>
+      <c r="F7" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F6" t="str">
-        <v>Pacific Motorway</v>
-      </c>
-      <c r="G6" t="str">
-        <v>M1</v>
-      </c>
-      <c r="H6" t="str">
+      <c r="G7" t="str">
+        <v>Bridge Street</v>
+      </c>
+      <c r="H7" t="str">
+        <v>B8</v>
+      </c>
+      <c r="I7" t="str">
         <v>NSW</v>
       </c>
-      <c r="I6" t="str">
-        <v>Sydney Metro</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Central Coast</v>
-      </c>
-      <c r="K6" t="str">
-        <v>-33.512800</v>
-      </c>
-      <c r="L6" t="str">
-        <v>151.241700</v>
-      </c>
-      <c r="M6" t="str">
-        <v>Mooney Mooney Creek</v>
-      </c>
-      <c r="N6" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O6" t="str">
-        <v>Transurban</v>
-      </c>
-      <c r="P6" t="str">
-        <v>Box Girder Bridge</v>
-      </c>
-      <c r="Q6">
-        <v>1986</v>
-      </c>
-      <c r="R6" t="str">
+      <c r="J7" t="str">
+        <v>Sydney Metropolitan</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Westbrook</v>
+      </c>
+      <c r="L7">
+        <v>-33.5487</v>
+      </c>
+      <c r="M7">
+        <v>150.7482</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Greywood River</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Westbrook Shire Council</v>
+      </c>
+      <c r="P7" t="str">
+        <v>Westbrook Shire Council</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>Cable-stayed Bridge</v>
+      </c>
+      <c r="R7">
+        <v>2018</v>
+      </c>
+      <c r="S7" t="str">
         <v>SM1600</v>
       </c>
-      <c r="S6" t="str">
+      <c r="T7" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T6" t="str">
-        <v>67.00</v>
-      </c>
-      <c r="U6" t="str">
-        <v>240.00</v>
-      </c>
-      <c r="V6" t="str">
-        <v>Concrete</v>
-      </c>
-      <c r="W6">
+      <c r="U7">
+        <v>11.8</v>
+      </c>
+      <c r="V7">
+        <v>140</v>
+      </c>
+      <c r="W7" t="str">
+        <v>Concrete and Steel</v>
+      </c>
+      <c r="X7">
+        <v>3</v>
+      </c>
+      <c r="Y7">
+        <v>320</v>
+      </c>
+      <c r="Z7">
+        <v>14.5</v>
+      </c>
+      <c r="AA7">
         <v>2</v>
       </c>
-      <c r="X6" t="str">
-        <v>292.00</v>
-      </c>
-      <c r="Y6" t="str">
-        <v>13.20</v>
-      </c>
-      <c r="Z6">
-        <v>4</v>
-      </c>
-      <c r="AA6" t="str">
-        <v>Good</v>
-      </c>
-      <c r="AB6">
-        <v>8</v>
-      </c>
-      <c r="AC6">
-        <v>8</v>
-      </c>
-      <c r="AD6" t="str">
+      <c r="AB7" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>10</v>
+      </c>
+      <c r="AE7" t="str">
         <v>Unrestricted</v>
       </c>
-      <c r="AE6" t="str">
+      <c r="AF7" t="str">
         <v>AS 5100</v>
       </c>
-      <c r="AF6" t="str">
+      <c r="AG7" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG6" t="str">
-        <v/>
-      </c>
-      <c r="AH6" t="str">
-        <v/>
-      </c>
-      <c r="AI6" t="str">
-        <v/>
-      </c>
-      <c r="AJ6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="str">
-        <v>One of Australia's highest bridges at 67m. Critical freight link on Pacific Highway corridor.</v>
-      </c>
-      <c r="AM6" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN6" t="str">
-        <v>Low</v>
-      </c>
-      <c r="AO6" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="AP6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="str">
-        <v>2025-09-12</v>
-      </c>
-      <c r="AR6" t="str">
-        <v>40.00</v>
-      </c>
-      <c r="AS6" t="str">
-        <v/>
-      </c>
-      <c r="AT6" t="str">
-        <v/>
-      </c>
-      <c r="AU6">
-        <v>85000</v>
-      </c>
-      <c r="AV6" t="str">
-        <v>22.00</v>
-      </c>
-      <c r="AW6" t="str">
-        <v/>
-      </c>
-      <c r="AX6" t="str">
-        <v/>
-      </c>
-      <c r="AY6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ6" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA6" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB6" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC6" t="str">
-        <v>DEMO</v>
-      </c>
-      <c r="BD6" t="str">
-        <v/>
-      </c>
-      <c r="BE6" t="str">
-        <v/>
-      </c>
-      <c r="BF6" t="str">
-        <v/>
-      </c>
-      <c r="BG6" t="str">
-        <v/>
-      </c>
-      <c r="BH6" t="str">
-        <v>{"type":"LineString","coordinates":[[151.239,-33.513],[151.244,-33.513]]}</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>1006</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v>BRG-NSW-SYD-006</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Windsor Bridge</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Road Bridge</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Bridge Street</v>
-      </c>
-      <c r="G7" t="str">
-        <v>B8</v>
-      </c>
-      <c r="H7" t="str">
-        <v>NSW</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Sydney Metro</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Hawkesbury</v>
-      </c>
-      <c r="K7" t="str">
-        <v>-33.614800</v>
-      </c>
-      <c r="L7" t="str">
-        <v>150.812800</v>
-      </c>
-      <c r="M7" t="str">
-        <v>Hawkesbury River</v>
-      </c>
-      <c r="N7" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O7" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P7" t="str">
-        <v>Cable-stayed Bridge</v>
-      </c>
-      <c r="Q7">
-        <v>2018</v>
-      </c>
-      <c r="R7" t="str">
-        <v>SM1600</v>
-      </c>
-      <c r="S7" t="str">
-        <v>AS5100</v>
-      </c>
-      <c r="T7" t="str">
-        <v>11.80</v>
-      </c>
-      <c r="U7" t="str">
-        <v>140.00</v>
-      </c>
-      <c r="V7" t="str">
-        <v>Concrete and Steel</v>
-      </c>
-      <c r="W7">
-        <v>3</v>
-      </c>
-      <c r="X7" t="str">
-        <v>320.00</v>
-      </c>
-      <c r="Y7" t="str">
-        <v>14.50</v>
-      </c>
-      <c r="Z7">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="str">
-        <v>Excellent</v>
-      </c>
-      <c r="AB7">
-        <v>10</v>
-      </c>
-      <c r="AC7">
-        <v>10</v>
-      </c>
-      <c r="AD7" t="str">
-        <v>Unrestricted</v>
-      </c>
-      <c r="AE7" t="str">
-        <v>AS 5100</v>
-      </c>
-      <c r="AF7" t="str">
-        <v>Zone 1</v>
-      </c>
-      <c r="AG7" t="str">
-        <v/>
       </c>
       <c r="AH7" t="str">
         <v/>
@@ -2828,55 +2857,55 @@
         <v>New 2018 replacement. Critical flood-immunity bridge — designed to 1 in 100-year ARI. Elevated 4m above original.</v>
       </c>
       <c r="AM7" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN7" t="str">
-        <v>High</v>
-      </c>
-      <c r="AO7" t="str">
         <v>2025-11-01</v>
       </c>
-      <c r="AP7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ7" t="str">
+      <c r="AO7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="str">
         <v>2025-11-05</v>
       </c>
+      <c r="AQ7">
+        <v>45</v>
+      </c>
       <c r="AR7" t="str">
-        <v>45.00</v>
+        <v/>
       </c>
       <c r="AS7" t="str">
         <v/>
       </c>
-      <c r="AT7" t="str">
-        <v/>
+      <c r="AT7">
+        <v>18000</v>
       </c>
       <c r="AU7">
-        <v>18000</v>
+        <v>12</v>
       </c>
       <c r="AV7" t="str">
-        <v>12.00</v>
+        <v/>
       </c>
       <c r="AW7" t="str">
         <v/>
       </c>
-      <c r="AX7" t="str">
-        <v/>
+      <c r="AX7" t="b">
+        <v>1</v>
       </c>
       <c r="AY7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA7" t="b">
         <v>1</v>
       </c>
-      <c r="BB7" t="b">
-        <v>1</v>
+      <c r="BB7" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC7" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD7" t="str">
         <v/>
@@ -2888,111 +2917,117 @@
         <v/>
       </c>
       <c r="BG7" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[150.746,-33.549],[150.751,-33.549]]}</v>
       </c>
       <c r="BH7" t="str">
-        <v>{"type":"LineString","coordinates":[[150.810,-33.615],[150.815,-33.615]]}</v>
+        <v/>
+      </c>
+      <c r="BI7" t="str">
+        <v/>
+      </c>
+      <c r="BJ7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>1007</v>
+      <c r="A8" t="str">
+        <v/>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
         <v>BRG-NSW-SYD-007</v>
       </c>
-      <c r="D8" t="str">
-        <v>Ryde Bridge</v>
-      </c>
       <c r="E8" t="str">
+        <v>Tarlington Bridge</v>
+      </c>
+      <c r="F8" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F8" t="str">
-        <v>Ryde Bridge Road</v>
-      </c>
       <c r="G8" t="str">
+        <v>Tarlington Road</v>
+      </c>
+      <c r="H8" t="str">
         <v>B87</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>NSW</v>
       </c>
-      <c r="I8" t="str">
-        <v>Sydney Metro</v>
-      </c>
       <c r="J8" t="str">
-        <v>City of Ryde</v>
+        <v>Sydney Metropolitan</v>
       </c>
       <c r="K8" t="str">
-        <v>-33.823200</v>
-      </c>
-      <c r="L8" t="str">
-        <v>151.094100</v>
-      </c>
-      <c r="M8" t="str">
-        <v>Parramatta River</v>
+        <v>Riverton</v>
+      </c>
+      <c r="L8">
+        <v>-33.7689</v>
+      </c>
+      <c r="M8">
+        <v>151.0526</v>
       </c>
       <c r="N8" t="str">
-        <v>Transport for NSW</v>
+        <v>Greywood River</v>
       </c>
       <c r="O8" t="str">
-        <v>Transport for NSW</v>
+        <v>Riverton City Council</v>
       </c>
       <c r="P8" t="str">
+        <v>Riverton City Council</v>
+      </c>
+      <c r="Q8" t="str">
         <v>Truss Bridge</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>1935</v>
       </c>
-      <c r="R8" t="str">
+      <c r="S8" t="str">
         <v>T44</v>
       </c>
-      <c r="S8" t="str">
+      <c r="T8" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T8" t="str">
-        <v>9.50</v>
-      </c>
-      <c r="U8" t="str">
-        <v>98.00</v>
-      </c>
-      <c r="V8" t="str">
+      <c r="U8">
+        <v>9.5</v>
+      </c>
+      <c r="V8">
+        <v>98</v>
+      </c>
+      <c r="W8" t="str">
         <v>Steel</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>3</v>
       </c>
-      <c r="X8" t="str">
-        <v>311.00</v>
-      </c>
-      <c r="Y8" t="str">
-        <v>10.20</v>
+      <c r="Y8">
+        <v>311</v>
       </c>
       <c r="Z8">
+        <v>10.2</v>
+      </c>
+      <c r="AA8">
         <v>2</v>
       </c>
-      <c r="AA8" t="str">
-        <v>Poor</v>
-      </c>
-      <c r="AB8">
+      <c r="AB8" t="str">
+        <v>4</v>
+      </c>
+      <c r="AC8">
+        <v>4</v>
+      </c>
+      <c r="AD8">
         <v>3</v>
       </c>
-      <c r="AC8">
-        <v>3</v>
-      </c>
-      <c r="AD8" t="str">
+      <c r="AE8" t="str">
         <v>Restricted</v>
       </c>
-      <c r="AE8" t="str">
+      <c r="AF8" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF8" t="str">
+      <c r="AG8" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG8" t="str">
-        <v/>
       </c>
       <c r="AH8" t="str">
         <v/>
@@ -3010,40 +3045,40 @@
         <v>90-year-old steel truss with significant section loss on lower chord members. Load restriction in place. Replacement planned 2027.</v>
       </c>
       <c r="AM8" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN8" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO8" t="str">
         <v>2025-07-22</v>
       </c>
-      <c r="AP8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="str">
-        <v/>
+      <c r="AO8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="str">
+        <v/>
+      </c>
+      <c r="AQ8">
+        <v>18</v>
       </c>
       <c r="AR8" t="str">
-        <v>18.00</v>
+        <v/>
       </c>
       <c r="AS8" t="str">
         <v/>
       </c>
-      <c r="AT8" t="str">
-        <v/>
+      <c r="AT8">
+        <v>22000</v>
       </c>
       <c r="AU8">
-        <v>22000</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="str">
-        <v>6.00</v>
+        <v/>
       </c>
       <c r="AW8" t="str">
         <v/>
       </c>
-      <c r="AX8" t="str">
-        <v/>
+      <c r="AX8" t="b">
+        <v>0</v>
       </c>
       <c r="AY8" t="b">
         <v>0</v>
@@ -3054,11 +3089,11 @@
       <c r="BA8" t="b">
         <v>0</v>
       </c>
-      <c r="BB8" t="b">
-        <v>0</v>
+      <c r="BB8" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC8" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD8" t="str">
         <v/>
@@ -3070,111 +3105,117 @@
         <v/>
       </c>
       <c r="BG8" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[151.049,-33.769],[151.055,-33.769]]}</v>
       </c>
       <c r="BH8" t="str">
-        <v>{"type":"LineString","coordinates":[[151.091,-33.823],[151.097,-33.823]]}</v>
+        <v/>
+      </c>
+      <c r="BI8" t="str">
+        <v/>
+      </c>
+      <c r="BJ8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>1008</v>
+      <c r="A9" t="str">
+        <v/>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
         <v>BRG-NSW-HUN-001</v>
       </c>
-      <c r="D9" t="str">
-        <v>Hexham Bridge</v>
-      </c>
       <c r="E9" t="str">
+        <v>Heaton Bascule Bridge</v>
+      </c>
+      <c r="F9" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F9" t="str">
-        <v>Pacific Highway</v>
-      </c>
       <c r="G9" t="str">
+        <v>Coastal Highway</v>
+      </c>
+      <c r="H9" t="str">
         <v>A1</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>NSW</v>
       </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
         <v>Hunter</v>
       </c>
-      <c r="J9" t="str">
-        <v>Port Stephens</v>
-      </c>
       <c r="K9" t="str">
-        <v>-32.842600</v>
-      </c>
-      <c r="L9" t="str">
-        <v>151.686200</v>
-      </c>
-      <c r="M9" t="str">
-        <v>Hunter River</v>
+        <v>Port Heaton</v>
+      </c>
+      <c r="L9">
+        <v>-32.8964</v>
+      </c>
+      <c r="M9">
+        <v>151.6128</v>
       </c>
       <c r="N9" t="str">
-        <v>Transport for NSW</v>
+        <v>Heaton River</v>
       </c>
       <c r="O9" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="P9" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q9" t="str">
         <v>Bascule Bridge</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>1975</v>
       </c>
-      <c r="R9" t="str">
+      <c r="S9" t="str">
         <v>T44</v>
       </c>
-      <c r="S9" t="str">
+      <c r="T9" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T9" t="str">
-        <v>4.60</v>
-      </c>
-      <c r="U9" t="str">
-        <v>45.70</v>
-      </c>
-      <c r="V9" t="str">
+      <c r="U9">
+        <v>4.6</v>
+      </c>
+      <c r="V9">
+        <v>45.7</v>
+      </c>
+      <c r="W9" t="str">
         <v>Steel</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <v>7</v>
       </c>
-      <c r="X9" t="str">
-        <v>322.00</v>
-      </c>
-      <c r="Y9" t="str">
-        <v>12.00</v>
+      <c r="Y9">
+        <v>322</v>
       </c>
       <c r="Z9">
+        <v>12</v>
+      </c>
+      <c r="AA9">
         <v>2</v>
       </c>
-      <c r="AA9" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB9">
+      <c r="AB9" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC9">
+        <v>3</v>
+      </c>
+      <c r="AD9">
         <v>5</v>
       </c>
-      <c r="AC9">
-        <v>5</v>
-      </c>
-      <c r="AD9" t="str">
+      <c r="AE9" t="str">
         <v>Restricted</v>
       </c>
-      <c r="AE9" t="str">
+      <c r="AF9" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF9" t="str">
+      <c r="AG9" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG9" t="str">
-        <v/>
       </c>
       <c r="AH9" t="str">
         <v/>
@@ -3192,55 +3233,55 @@
         <v>Bascule opening bridge on major freight corridor. Scour monitoring programme active. Flood affected Jan 2023.</v>
       </c>
       <c r="AM9" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN9" t="str">
-        <v>High</v>
-      </c>
-      <c r="AO9" t="str">
         <v>2025-08-30</v>
       </c>
-      <c r="AP9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ9" t="str">
+      <c r="AO9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="str">
         <v>2025-09-10</v>
       </c>
+      <c r="AQ9">
+        <v>25</v>
+      </c>
       <c r="AR9" t="str">
-        <v>25.00</v>
+        <v/>
       </c>
       <c r="AS9" t="str">
         <v/>
       </c>
-      <c r="AT9" t="str">
-        <v/>
+      <c r="AT9">
+        <v>38000</v>
       </c>
       <c r="AU9">
-        <v>38000</v>
+        <v>19</v>
       </c>
       <c r="AV9" t="str">
-        <v>19.00</v>
+        <v/>
       </c>
       <c r="AW9" t="str">
         <v/>
       </c>
-      <c r="AX9" t="str">
-        <v/>
+      <c r="AX9" t="b">
+        <v>1</v>
       </c>
       <c r="AY9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="b">
         <v>0</v>
       </c>
       <c r="BA9" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="BB9" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC9" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD9" t="str">
         <v/>
@@ -3252,111 +3293,117 @@
         <v/>
       </c>
       <c r="BG9" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[151.610,-32.896],[151.616,-32.896]]}</v>
       </c>
       <c r="BH9" t="str">
-        <v>{"type":"LineString","coordinates":[[151.683,-32.843],[151.689,-32.843]]}</v>
+        <v/>
+      </c>
+      <c r="BI9" t="str">
+        <v/>
+      </c>
+      <c r="BJ9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>1009</v>
+      <c r="A10" t="str">
+        <v/>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
         <v>BRG-NSW-HUN-002</v>
       </c>
-      <c r="D10" t="str">
-        <v>Maitland Rail Bridge</v>
-      </c>
       <c r="E10" t="str">
+        <v>Milfield Truss Bridge</v>
+      </c>
+      <c r="F10" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F10" t="str">
-        <v>Hunter Street</v>
-      </c>
       <c r="G10" t="str">
+        <v>Valley Street</v>
+      </c>
+      <c r="H10" t="str">
         <v>B64</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>NSW</v>
       </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
         <v>Hunter</v>
       </c>
-      <c r="J10" t="str">
-        <v>Maitland</v>
-      </c>
       <c r="K10" t="str">
-        <v>-32.730800</v>
-      </c>
-      <c r="L10" t="str">
-        <v>151.554200</v>
-      </c>
-      <c r="M10" t="str">
-        <v>Hunter River</v>
+        <v>Milfield</v>
+      </c>
+      <c r="L10">
+        <v>-32.7042</v>
+      </c>
+      <c r="M10">
+        <v>151.4986</v>
       </c>
       <c r="N10" t="str">
-        <v>Transport for NSW</v>
+        <v>Heaton River</v>
       </c>
       <c r="O10" t="str">
-        <v>Transport for NSW</v>
+        <v>Milfield Shire Council</v>
       </c>
       <c r="P10" t="str">
+        <v>Milfield Shire Council</v>
+      </c>
+      <c r="Q10" t="str">
         <v>Truss Bridge</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>1896</v>
       </c>
-      <c r="R10" t="str">
+      <c r="S10" t="str">
         <v>T44</v>
       </c>
-      <c r="S10" t="str">
+      <c r="T10" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T10" t="str">
-        <v>7.20</v>
-      </c>
-      <c r="U10" t="str">
-        <v>80.00</v>
-      </c>
-      <c r="V10" t="str">
+      <c r="U10">
+        <v>7.2</v>
+      </c>
+      <c r="V10">
+        <v>80</v>
+      </c>
+      <c r="W10" t="str">
         <v>Steel</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>4</v>
       </c>
-      <c r="X10" t="str">
-        <v>352.00</v>
-      </c>
-      <c r="Y10" t="str">
-        <v>8.40</v>
+      <c r="Y10">
+        <v>352</v>
       </c>
       <c r="Z10">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="str">
-        <v>Poor</v>
-      </c>
-      <c r="AB10">
+        <v>8.4</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>5</v>
+      </c>
+      <c r="AC10">
+        <v>5</v>
+      </c>
+      <c r="AD10">
         <v>2</v>
       </c>
-      <c r="AC10">
-        <v>2</v>
-      </c>
-      <c r="AD10" t="str">
+      <c r="AE10" t="str">
         <v>Restricted</v>
       </c>
-      <c r="AE10" t="str">
+      <c r="AF10" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF10" t="str">
+      <c r="AG10" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG10" t="str">
-        <v/>
       </c>
       <c r="AH10" t="str">
         <v/>
@@ -3374,40 +3421,40 @@
         <v>130-year-old riveted steel truss. Emergency load limit 12t. Critical scour undermining at Pier 2. Replacement business case submitted.</v>
       </c>
       <c r="AM10" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN10" t="str">
-        <v>High</v>
-      </c>
-      <c r="AO10" t="str">
         <v>2025-05-14</v>
       </c>
-      <c r="AP10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="str">
-        <v/>
+      <c r="AO10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="str">
+        <v/>
+      </c>
+      <c r="AQ10">
+        <v>12</v>
       </c>
       <c r="AR10" t="str">
-        <v>12.00</v>
+        <v/>
       </c>
       <c r="AS10" t="str">
         <v/>
       </c>
-      <c r="AT10" t="str">
-        <v/>
+      <c r="AT10">
+        <v>8500</v>
       </c>
       <c r="AU10">
-        <v>8500</v>
+        <v>4.5</v>
       </c>
       <c r="AV10" t="str">
-        <v>4.50</v>
+        <v/>
       </c>
       <c r="AW10" t="str">
         <v/>
       </c>
-      <c r="AX10" t="str">
-        <v/>
+      <c r="AX10" t="b">
+        <v>0</v>
       </c>
       <c r="AY10" t="b">
         <v>0</v>
@@ -3418,11 +3465,11 @@
       <c r="BA10" t="b">
         <v>0</v>
       </c>
-      <c r="BB10" t="b">
-        <v>0</v>
+      <c r="BB10" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC10" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD10" t="str">
         <v/>
@@ -3434,111 +3481,117 @@
         <v/>
       </c>
       <c r="BG10" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[151.496,-32.704],[151.502,-32.704]]}</v>
       </c>
       <c r="BH10" t="str">
-        <v>{"type":"LineString","coordinates":[[151.551,-32.731],[151.557,-32.731]]}</v>
+        <v/>
+      </c>
+      <c r="BI10" t="str">
+        <v/>
+      </c>
+      <c r="BJ10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>1010</v>
+      <c r="A11" t="str">
+        <v/>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
         <v>BRG-NSW-HUN-003</v>
       </c>
-      <c r="D11" t="str">
-        <v>Karuah River Bridge</v>
-      </c>
       <c r="E11" t="str">
+        <v>Carwell River Bridge</v>
+      </c>
+      <c r="F11" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F11" t="str">
-        <v>Pacific Highway</v>
-      </c>
       <c r="G11" t="str">
+        <v>Coastal Highway</v>
+      </c>
+      <c r="H11" t="str">
         <v>A1</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>NSW</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
         <v>Hunter</v>
       </c>
-      <c r="J11" t="str">
-        <v>Port Stephens</v>
-      </c>
       <c r="K11" t="str">
-        <v>-32.659000</v>
-      </c>
-      <c r="L11" t="str">
-        <v>151.955700</v>
-      </c>
-      <c r="M11" t="str">
-        <v>Karuah River</v>
+        <v>Port Heaton</v>
+      </c>
+      <c r="L11">
+        <v>-32.6124</v>
+      </c>
+      <c r="M11">
+        <v>151.9923</v>
       </c>
       <c r="N11" t="str">
-        <v>Transport for NSW</v>
+        <v>Carwell River</v>
       </c>
       <c r="O11" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="P11" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q11" t="str">
         <v>Prestressed Concrete Girder</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>1997</v>
       </c>
-      <c r="R11" t="str">
+      <c r="S11" t="str">
         <v>SM1600</v>
       </c>
-      <c r="S11" t="str">
+      <c r="T11" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T11" t="str">
-        <v>8.50</v>
-      </c>
-      <c r="U11" t="str">
-        <v>40.00</v>
-      </c>
-      <c r="V11" t="str">
+      <c r="U11">
+        <v>8.5</v>
+      </c>
+      <c r="V11">
+        <v>40</v>
+      </c>
+      <c r="W11" t="str">
         <v>Concrete</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>8</v>
       </c>
-      <c r="X11" t="str">
-        <v>328.00</v>
-      </c>
-      <c r="Y11" t="str">
-        <v>13.40</v>
+      <c r="Y11">
+        <v>328</v>
       </c>
       <c r="Z11">
+        <v>13.4</v>
+      </c>
+      <c r="AA11">
         <v>2</v>
       </c>
-      <c r="AA11" t="str">
-        <v>Good</v>
-      </c>
-      <c r="AB11">
-        <v>7</v>
+      <c r="AB11" t="str">
+        <v>2</v>
       </c>
       <c r="AC11">
+        <v>2</v>
+      </c>
+      <c r="AD11">
         <v>8</v>
       </c>
-      <c r="AD11" t="str">
+      <c r="AE11" t="str">
         <v>Unrestricted</v>
       </c>
-      <c r="AE11" t="str">
+      <c r="AF11" t="str">
         <v>AS 5100</v>
       </c>
-      <c r="AF11" t="str">
+      <c r="AG11" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG11" t="str">
-        <v/>
       </c>
       <c r="AH11" t="str">
         <v/>
@@ -3556,40 +3609,40 @@
         <v>Modern PSC girder bridge. Bypass highway alignment. Regular heavy vehicle use.</v>
       </c>
       <c r="AM11" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN11" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO11" t="str">
         <v>2025-10-18</v>
       </c>
-      <c r="AP11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ11" t="str">
+      <c r="AO11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="str">
         <v>2025-10-25</v>
       </c>
+      <c r="AQ11">
+        <v>38.5</v>
+      </c>
       <c r="AR11" t="str">
-        <v>38.50</v>
+        <v/>
       </c>
       <c r="AS11" t="str">
         <v/>
       </c>
-      <c r="AT11" t="str">
-        <v/>
+      <c r="AT11">
+        <v>18000</v>
       </c>
       <c r="AU11">
-        <v>18000</v>
+        <v>24</v>
       </c>
       <c r="AV11" t="str">
-        <v>24.00</v>
+        <v/>
       </c>
       <c r="AW11" t="str">
         <v/>
       </c>
-      <c r="AX11" t="str">
-        <v/>
+      <c r="AX11" t="b">
+        <v>1</v>
       </c>
       <c r="AY11" t="b">
         <v>1</v>
@@ -3600,11 +3653,11 @@
       <c r="BA11" t="b">
         <v>1</v>
       </c>
-      <c r="BB11" t="b">
-        <v>1</v>
+      <c r="BB11" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC11" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD11" t="str">
         <v/>
@@ -3616,111 +3669,117 @@
         <v/>
       </c>
       <c r="BG11" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[151.989,-32.612],[151.996,-32.612]]}</v>
       </c>
       <c r="BH11" t="str">
-        <v>{"type":"LineString","coordinates":[[151.952,-32.659],[151.959,-32.659]]}</v>
+        <v/>
+      </c>
+      <c r="BI11" t="str">
+        <v/>
+      </c>
+      <c r="BJ11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>1011</v>
+      <c r="A12" t="str">
+        <v/>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
         <v>BRG-NSW-NOR-001</v>
       </c>
-      <c r="D12" t="str">
-        <v>Grafton Bridge (Clarence River)</v>
-      </c>
       <c r="E12" t="str">
+        <v>Clarendon Bridge</v>
+      </c>
+      <c r="F12" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F12" t="str">
-        <v>Summerland Way</v>
-      </c>
       <c r="G12" t="str">
+        <v>Inland Way</v>
+      </c>
+      <c r="H12" t="str">
         <v>B65</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <v>NSW</v>
       </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
         <v>Northern NSW</v>
       </c>
-      <c r="J12" t="str">
-        <v>Clarence Valley</v>
-      </c>
       <c r="K12" t="str">
-        <v>-29.690700</v>
-      </c>
-      <c r="L12" t="str">
-        <v>152.931900</v>
-      </c>
-      <c r="M12" t="str">
-        <v>Clarence River</v>
+        <v>Clarendon Valley</v>
+      </c>
+      <c r="L12">
+        <v>-29.7486</v>
+      </c>
+      <c r="M12">
+        <v>152.8964</v>
       </c>
       <c r="N12" t="str">
-        <v>Transport for NSW</v>
+        <v>Clarendon River</v>
       </c>
       <c r="O12" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="P12" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q12" t="str">
         <v>Arch Truss Bridge</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>1932</v>
       </c>
-      <c r="R12" t="str">
+      <c r="S12" t="str">
         <v>T44</v>
       </c>
-      <c r="S12" t="str">
+      <c r="T12" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T12" t="str">
-        <v>14.30</v>
-      </c>
-      <c r="U12" t="str">
-        <v>118.00</v>
-      </c>
-      <c r="V12" t="str">
+      <c r="U12">
+        <v>14.3</v>
+      </c>
+      <c r="V12">
+        <v>118</v>
+      </c>
+      <c r="W12" t="str">
         <v>Steel</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <v>5</v>
       </c>
-      <c r="X12" t="str">
-        <v>634.00</v>
-      </c>
-      <c r="Y12" t="str">
-        <v>9.80</v>
+      <c r="Y12">
+        <v>634</v>
       </c>
       <c r="Z12">
+        <v>9.8</v>
+      </c>
+      <c r="AA12">
         <v>2</v>
       </c>
-      <c r="AA12" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB12">
+      <c r="AB12" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC12">
+        <v>3</v>
+      </c>
+      <c r="AD12">
         <v>5</v>
       </c>
-      <c r="AC12">
-        <v>5</v>
-      </c>
-      <c r="AD12" t="str">
+      <c r="AE12" t="str">
         <v>Restricted</v>
       </c>
-      <c r="AE12" t="str">
+      <c r="AF12" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF12" t="str">
+      <c r="AG12" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG12" t="str">
-        <v/>
       </c>
       <c r="AH12" t="str">
         <v/>
@@ -3738,43 +3797,43 @@
         <v>Heritage swing-span truss. Shares dual-level with railway. Flood affected Feb 2022. Scour protection works 2024.</v>
       </c>
       <c r="AM12" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN12" t="str">
-        <v>High</v>
-      </c>
-      <c r="AO12" t="str">
         <v>2025-09-25</v>
       </c>
-      <c r="AP12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ12" t="str">
+      <c r="AO12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP12" t="str">
         <v>2025-10-01</v>
       </c>
+      <c r="AQ12">
+        <v>26</v>
+      </c>
       <c r="AR12" t="str">
-        <v>26.00</v>
+        <v/>
       </c>
       <c r="AS12" t="str">
         <v/>
       </c>
-      <c r="AT12" t="str">
-        <v/>
+      <c r="AT12">
+        <v>12000</v>
       </c>
       <c r="AU12">
-        <v>12000</v>
+        <v>18</v>
       </c>
       <c r="AV12" t="str">
-        <v>18.00</v>
+        <v/>
       </c>
       <c r="AW12" t="str">
         <v/>
       </c>
-      <c r="AX12" t="str">
-        <v/>
+      <c r="AX12" t="b">
+        <v>1</v>
       </c>
       <c r="AY12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="b">
         <v>0</v>
@@ -3782,11 +3841,11 @@
       <c r="BA12" t="b">
         <v>0</v>
       </c>
-      <c r="BB12" t="b">
-        <v>0</v>
+      <c r="BB12" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC12" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD12" t="str">
         <v/>
@@ -3798,111 +3857,117 @@
         <v/>
       </c>
       <c r="BG12" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[152.893,-29.749],[152.900,-29.749]]}</v>
       </c>
       <c r="BH12" t="str">
-        <v>{"type":"LineString","coordinates":[[152.928,-29.691],[152.935,-29.691]]}</v>
+        <v/>
+      </c>
+      <c r="BI12" t="str">
+        <v/>
+      </c>
+      <c r="BJ12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>1012</v>
+      <c r="A13" t="str">
+        <v/>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
         <v>BRG-NSW-NOR-002</v>
       </c>
-      <c r="D13" t="str">
-        <v>Manning River Bridge (Taree)</v>
-      </c>
       <c r="E13" t="str">
+        <v>Tallowood River Bridge</v>
+      </c>
+      <c r="F13" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F13" t="str">
-        <v>Pacific Highway</v>
-      </c>
       <c r="G13" t="str">
+        <v>Coastal Highway</v>
+      </c>
+      <c r="H13" t="str">
         <v>A1</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v>NSW</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
         <v>Northern NSW</v>
       </c>
-      <c r="J13" t="str">
-        <v>Mid-Coast</v>
-      </c>
       <c r="K13" t="str">
-        <v>-31.902100</v>
-      </c>
-      <c r="L13" t="str">
-        <v>152.451800</v>
-      </c>
-      <c r="M13" t="str">
-        <v>Manning River</v>
+        <v>Tallowood</v>
+      </c>
+      <c r="L13">
+        <v>-31.8563</v>
+      </c>
+      <c r="M13">
+        <v>152.4048</v>
       </c>
       <c r="N13" t="str">
-        <v>Transport for NSW</v>
+        <v>Tallowood River</v>
       </c>
       <c r="O13" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="P13" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q13" t="str">
         <v>Prestressed Concrete Girder</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>1981</v>
       </c>
-      <c r="R13" t="str">
+      <c r="S13" t="str">
         <v>T44</v>
       </c>
-      <c r="S13" t="str">
+      <c r="T13" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T13" t="str">
-        <v>8.80</v>
-      </c>
-      <c r="U13" t="str">
-        <v>38.00</v>
-      </c>
-      <c r="V13" t="str">
+      <c r="U13">
+        <v>8.8</v>
+      </c>
+      <c r="V13">
+        <v>38</v>
+      </c>
+      <c r="W13" t="str">
         <v>Concrete</v>
       </c>
-      <c r="W13">
+      <c r="X13">
         <v>10</v>
       </c>
-      <c r="X13" t="str">
-        <v>396.00</v>
-      </c>
-      <c r="Y13" t="str">
-        <v>12.20</v>
+      <c r="Y13">
+        <v>396</v>
       </c>
       <c r="Z13">
+        <v>12.2</v>
+      </c>
+      <c r="AA13">
         <v>2</v>
       </c>
-      <c r="AA13" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB13">
+      <c r="AB13" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC13">
+        <v>3</v>
+      </c>
+      <c r="AD13">
         <v>6</v>
       </c>
-      <c r="AC13">
-        <v>6</v>
-      </c>
-      <c r="AD13" t="str">
+      <c r="AE13" t="str">
         <v>Unrestricted</v>
       </c>
-      <c r="AE13" t="str">
+      <c r="AF13" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF13" t="str">
+      <c r="AG13" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG13" t="str">
-        <v/>
       </c>
       <c r="AH13" t="str">
         <v/>
@@ -3920,55 +3985,55 @@
         <v>Key north coast freight route. Deck resurfacing 2022. Substructure inspection due 2026.</v>
       </c>
       <c r="AM13" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN13" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO13" t="str">
         <v>2025-07-08</v>
       </c>
-      <c r="AP13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ13" t="str">
+      <c r="AO13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="str">
         <v>2025-07-15</v>
       </c>
+      <c r="AQ13">
+        <v>34</v>
+      </c>
       <c r="AR13" t="str">
-        <v>34.00</v>
+        <v/>
       </c>
       <c r="AS13" t="str">
         <v/>
       </c>
-      <c r="AT13" t="str">
-        <v/>
+      <c r="AT13">
+        <v>24000</v>
       </c>
       <c r="AU13">
-        <v>24000</v>
+        <v>21</v>
       </c>
       <c r="AV13" t="str">
-        <v>21.00</v>
+        <v/>
       </c>
       <c r="AW13" t="str">
         <v/>
       </c>
-      <c r="AX13" t="str">
-        <v/>
+      <c r="AX13" t="b">
+        <v>1</v>
       </c>
       <c r="AY13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA13" t="b">
         <v>1</v>
       </c>
-      <c r="BB13" t="b">
-        <v>1</v>
+      <c r="BB13" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC13" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD13" t="str">
         <v/>
@@ -3980,111 +4045,117 @@
         <v/>
       </c>
       <c r="BG13" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[152.402,-31.856],[152.408,-31.856]]}</v>
       </c>
       <c r="BH13" t="str">
-        <v>{"type":"LineString","coordinates":[[152.448,-31.902],[152.455,-31.902]]}</v>
+        <v/>
+      </c>
+      <c r="BI13" t="str">
+        <v/>
+      </c>
+      <c r="BJ13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>1013</v>
+      <c r="A14" t="str">
+        <v/>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
         <v>BRG-NSW-NOR-003</v>
       </c>
-      <c r="D14" t="str">
-        <v>Hastings River Bridge (Port Macquarie)</v>
-      </c>
       <c r="E14" t="str">
+        <v>Westhaven River Bridge</v>
+      </c>
+      <c r="F14" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F14" t="str">
-        <v>Oxley Highway</v>
-      </c>
       <c r="G14" t="str">
+        <v>Tableland Highway</v>
+      </c>
+      <c r="H14" t="str">
         <v>B56</v>
       </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
         <v>NSW</v>
       </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
         <v>Northern NSW</v>
       </c>
-      <c r="J14" t="str">
-        <v>Port Macquarie-Hastings</v>
-      </c>
       <c r="K14" t="str">
-        <v>-31.433900</v>
-      </c>
-      <c r="L14" t="str">
-        <v>152.904700</v>
-      </c>
-      <c r="M14" t="str">
-        <v>Hastings River</v>
+        <v>Westhaven</v>
+      </c>
+      <c r="L14">
+        <v>-31.4982</v>
+      </c>
+      <c r="M14">
+        <v>152.8524</v>
       </c>
       <c r="N14" t="str">
-        <v>Transport for NSW</v>
+        <v>Westhaven River</v>
       </c>
       <c r="O14" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="P14" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q14" t="str">
         <v>Prestressed Concrete Girder</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>1966</v>
       </c>
-      <c r="R14" t="str">
+      <c r="S14" t="str">
         <v>T44</v>
       </c>
-      <c r="S14" t="str">
+      <c r="T14" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T14" t="str">
-        <v>8.20</v>
-      </c>
-      <c r="U14" t="str">
-        <v>36.00</v>
-      </c>
-      <c r="V14" t="str">
+      <c r="U14">
+        <v>8.2</v>
+      </c>
+      <c r="V14">
+        <v>36</v>
+      </c>
+      <c r="W14" t="str">
         <v>Concrete</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <v>7</v>
       </c>
-      <c r="X14" t="str">
-        <v>267.00</v>
-      </c>
-      <c r="Y14" t="str">
-        <v>11.00</v>
+      <c r="Y14">
+        <v>267</v>
       </c>
       <c r="Z14">
+        <v>11</v>
+      </c>
+      <c r="AA14">
         <v>2</v>
       </c>
-      <c r="AA14" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB14">
+      <c r="AB14" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC14">
+        <v>3</v>
+      </c>
+      <c r="AD14">
         <v>5</v>
       </c>
-      <c r="AC14">
-        <v>5</v>
-      </c>
-      <c r="AD14" t="str">
+      <c r="AE14" t="str">
         <v>Restricted</v>
       </c>
-      <c r="AE14" t="str">
+      <c r="AF14" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF14" t="str">
+      <c r="AG14" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG14" t="str">
-        <v/>
       </c>
       <c r="AH14" t="str">
         <v/>
@@ -4102,55 +4173,55 @@
         <v>Ageing PSC structure approaching 60 years. Widening feasibility study in progress.</v>
       </c>
       <c r="AM14" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN14" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO14" t="str">
         <v>2025-06-19</v>
       </c>
-      <c r="AP14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ14" t="str">
+      <c r="AO14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="str">
         <v>2025-06-28</v>
       </c>
+      <c r="AQ14">
+        <v>28.5</v>
+      </c>
       <c r="AR14" t="str">
-        <v>28.50</v>
+        <v/>
       </c>
       <c r="AS14" t="str">
         <v/>
       </c>
-      <c r="AT14" t="str">
-        <v/>
+      <c r="AT14">
+        <v>16500</v>
       </c>
       <c r="AU14">
-        <v>16500</v>
+        <v>14</v>
       </c>
       <c r="AV14" t="str">
-        <v>14.00</v>
+        <v/>
       </c>
       <c r="AW14" t="str">
         <v/>
       </c>
-      <c r="AX14" t="str">
-        <v/>
+      <c r="AX14" t="b">
+        <v>1</v>
       </c>
       <c r="AY14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="b">
         <v>0</v>
       </c>
       <c r="BA14" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="BB14" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC14" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD14" t="str">
         <v/>
@@ -4162,111 +4233,117 @@
         <v/>
       </c>
       <c r="BG14" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[152.850,-31.498],[152.856,-31.498]]}</v>
       </c>
       <c r="BH14" t="str">
-        <v>{"type":"LineString","coordinates":[[152.901,-31.434],[152.908,-31.434]]}</v>
+        <v/>
+      </c>
+      <c r="BI14" t="str">
+        <v/>
+      </c>
+      <c r="BJ14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>1014</v>
+      <c r="A15" t="str">
+        <v/>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
         <v>BRG-NSW-NOR-004</v>
       </c>
-      <c r="D15" t="str">
-        <v>Macleay River Bridge (Kempsey)</v>
-      </c>
       <c r="E15" t="str">
+        <v>Greenbank River Bridge</v>
+      </c>
+      <c r="F15" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F15" t="str">
-        <v>Pacific Highway</v>
-      </c>
       <c r="G15" t="str">
+        <v>Coastal Highway</v>
+      </c>
+      <c r="H15" t="str">
         <v>A1</v>
       </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
         <v>NSW</v>
       </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
         <v>Northern NSW</v>
       </c>
-      <c r="J15" t="str">
-        <v>Kempsey</v>
-      </c>
       <c r="K15" t="str">
-        <v>-31.081700</v>
-      </c>
-      <c r="L15" t="str">
-        <v>152.832900</v>
-      </c>
-      <c r="M15" t="str">
-        <v>Macleay River</v>
+        <v>Greenbank</v>
+      </c>
+      <c r="L15">
+        <v>-31.1246</v>
+      </c>
+      <c r="M15">
+        <v>152.7862</v>
       </c>
       <c r="N15" t="str">
-        <v>Transport for NSW</v>
+        <v>Greenbank River</v>
       </c>
       <c r="O15" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="P15" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q15" t="str">
         <v>Truss Bridge</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>1966</v>
       </c>
-      <c r="R15" t="str">
+      <c r="S15" t="str">
         <v>T44</v>
       </c>
-      <c r="S15" t="str">
+      <c r="T15" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T15" t="str">
-        <v>10.60</v>
-      </c>
-      <c r="U15" t="str">
-        <v>95.00</v>
-      </c>
-      <c r="V15" t="str">
+      <c r="U15">
+        <v>10.6</v>
+      </c>
+      <c r="V15">
+        <v>95</v>
+      </c>
+      <c r="W15" t="str">
         <v>Steel</v>
       </c>
-      <c r="W15">
+      <c r="X15">
         <v>4</v>
       </c>
-      <c r="X15" t="str">
-        <v>410.00</v>
-      </c>
-      <c r="Y15" t="str">
-        <v>10.50</v>
+      <c r="Y15">
+        <v>410</v>
       </c>
       <c r="Z15">
+        <v>10.5</v>
+      </c>
+      <c r="AA15">
         <v>2</v>
       </c>
-      <c r="AA15" t="str">
-        <v>Poor</v>
-      </c>
-      <c r="AB15">
+      <c r="AB15" t="str">
         <v>4</v>
       </c>
       <c r="AC15">
         <v>4</v>
       </c>
-      <c r="AD15" t="str">
+      <c r="AD15">
+        <v>4</v>
+      </c>
+      <c r="AE15" t="str">
         <v>Restricted</v>
       </c>
-      <c r="AE15" t="str">
+      <c r="AF15" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF15" t="str">
+      <c r="AG15" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG15" t="str">
-        <v/>
       </c>
       <c r="AH15" t="str">
         <v/>
@@ -4284,43 +4361,43 @@
         <v>Major north coast freight constraint. Rated 22t GML. Business case for replacement approved 2024 — construction 2027-2030.</v>
       </c>
       <c r="AM15" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN15" t="str">
-        <v>High</v>
-      </c>
-      <c r="AO15" t="str">
         <v>2025-05-30</v>
       </c>
-      <c r="AP15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="str">
-        <v/>
+      <c r="AO15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="str">
+        <v/>
+      </c>
+      <c r="AQ15">
+        <v>22</v>
       </c>
       <c r="AR15" t="str">
-        <v>22.00</v>
+        <v/>
       </c>
       <c r="AS15" t="str">
         <v/>
       </c>
-      <c r="AT15" t="str">
-        <v/>
+      <c r="AT15">
+        <v>13500</v>
       </c>
       <c r="AU15">
-        <v>13500</v>
+        <v>20</v>
       </c>
       <c r="AV15" t="str">
-        <v>20.00</v>
+        <v/>
       </c>
       <c r="AW15" t="str">
         <v/>
       </c>
-      <c r="AX15" t="str">
-        <v/>
+      <c r="AX15" t="b">
+        <v>1</v>
       </c>
       <c r="AY15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="b">
         <v>0</v>
@@ -4328,11 +4405,11 @@
       <c r="BA15" t="b">
         <v>0</v>
       </c>
-      <c r="BB15" t="b">
-        <v>0</v>
+      <c r="BB15" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC15" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD15" t="str">
         <v/>
@@ -4344,111 +4421,117 @@
         <v/>
       </c>
       <c r="BG15" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[152.783,-31.125],[152.790,-31.125]]}</v>
       </c>
       <c r="BH15" t="str">
-        <v>{"type":"LineString","coordinates":[[152.829,-31.082],[152.836,-31.082]]}</v>
+        <v/>
+      </c>
+      <c r="BI15" t="str">
+        <v/>
+      </c>
+      <c r="BJ15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>1015</v>
+      <c r="A16" t="str">
+        <v/>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
         <v>BRG-NSW-NOR-005</v>
       </c>
-      <c r="D16" t="str">
-        <v>Bellinger River Bridge (Urunga)</v>
-      </c>
       <c r="E16" t="str">
+        <v>Fernleigh River Bridge</v>
+      </c>
+      <c r="F16" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F16" t="str">
-        <v>Pacific Highway</v>
-      </c>
       <c r="G16" t="str">
+        <v>Coastal Highway</v>
+      </c>
+      <c r="H16" t="str">
         <v>A1</v>
       </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
         <v>NSW</v>
       </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
         <v>Northern NSW</v>
       </c>
-      <c r="J16" t="str">
-        <v>Bellingen</v>
-      </c>
       <c r="K16" t="str">
-        <v>-30.492100</v>
-      </c>
-      <c r="L16" t="str">
-        <v>152.999800</v>
-      </c>
-      <c r="M16" t="str">
-        <v>Bellinger River</v>
+        <v>Fernleigh</v>
+      </c>
+      <c r="L16">
+        <v>-30.5487</v>
+      </c>
+      <c r="M16">
+        <v>152.9483</v>
       </c>
       <c r="N16" t="str">
-        <v>Transport for NSW</v>
+        <v>Fernleigh River</v>
       </c>
       <c r="O16" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="P16" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q16" t="str">
         <v>Prestressed Concrete Girder</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>1979</v>
       </c>
-      <c r="R16" t="str">
+      <c r="S16" t="str">
         <v>T44</v>
       </c>
-      <c r="S16" t="str">
+      <c r="T16" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T16" t="str">
-        <v>7.40</v>
-      </c>
-      <c r="U16" t="str">
-        <v>32.00</v>
-      </c>
-      <c r="V16" t="str">
+      <c r="U16">
+        <v>7.4</v>
+      </c>
+      <c r="V16">
+        <v>32</v>
+      </c>
+      <c r="W16" t="str">
         <v>Concrete</v>
       </c>
-      <c r="W16">
+      <c r="X16">
         <v>9</v>
       </c>
-      <c r="X16" t="str">
-        <v>302.00</v>
-      </c>
-      <c r="Y16" t="str">
-        <v>11.80</v>
+      <c r="Y16">
+        <v>302</v>
       </c>
       <c r="Z16">
+        <v>11.8</v>
+      </c>
+      <c r="AA16">
         <v>2</v>
       </c>
-      <c r="AA16" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB16">
+      <c r="AB16" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC16">
+        <v>3</v>
+      </c>
+      <c r="AD16">
         <v>6</v>
       </c>
-      <c r="AC16">
-        <v>6</v>
-      </c>
-      <c r="AD16" t="str">
+      <c r="AE16" t="str">
         <v>Unrestricted</v>
       </c>
-      <c r="AE16" t="str">
+      <c r="AF16" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF16" t="str">
+      <c r="AG16" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG16" t="str">
-        <v/>
       </c>
       <c r="AH16" t="str">
         <v/>
@@ -4466,899 +4549,929 @@
         <v>Flood-prone crossing — 1 in 10 ARI flood immunity. Deck waterproofing renewed 2021.</v>
       </c>
       <c r="AM16" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN16" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO16" t="str">
         <v>2025-08-11</v>
       </c>
-      <c r="AP16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ16" t="str">
+      <c r="AO16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="str">
         <v>2025-08-18</v>
       </c>
+      <c r="AQ16">
+        <v>33</v>
+      </c>
       <c r="AR16" t="str">
-        <v>33.00</v>
+        <v/>
       </c>
       <c r="AS16" t="str">
         <v/>
       </c>
-      <c r="AT16" t="str">
-        <v/>
+      <c r="AT16">
+        <v>9800</v>
       </c>
       <c r="AU16">
-        <v>9800</v>
+        <v>16.5</v>
       </c>
       <c r="AV16" t="str">
-        <v>16.50</v>
+        <v/>
       </c>
       <c r="AW16" t="str">
         <v/>
       </c>
-      <c r="AX16" t="str">
-        <v/>
+      <c r="AX16" t="b">
+        <v>1</v>
       </c>
       <c r="AY16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA16" t="b">
         <v>1</v>
       </c>
-      <c r="BB16" t="b">
-        <v>1</v>
+      <c r="BB16" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC16" t="str">
+        <v/>
+      </c>
+      <c r="BD16" t="str">
+        <v/>
+      </c>
+      <c r="BE16" t="str">
+        <v/>
+      </c>
+      <c r="BF16" t="str">
+        <v/>
+      </c>
+      <c r="BG16" t="str">
+        <v>{"type":"LineString","coordinates":[[152.945,-30.549],[152.952,-30.549]]}</v>
+      </c>
+      <c r="BH16" t="str">
+        <v/>
+      </c>
+      <c r="BI16" t="str">
+        <v/>
+      </c>
+      <c r="BJ16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v/>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>BRG-NSW-NEW-001</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Stonebrook River Bridge</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Road Bridge</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Commerce Street</v>
+      </c>
+      <c r="H17" t="str">
+        <v>B54</v>
+      </c>
+      <c r="I17" t="str">
+        <v>NSW</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Western NSW</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Stonebrook Regional</v>
+      </c>
+      <c r="L17">
+        <v>-32.2968</v>
+      </c>
+      <c r="M17">
+        <v>148.5124</v>
+      </c>
+      <c r="N17" t="str">
+        <v>Stonebrook River</v>
+      </c>
+      <c r="O17" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P17" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>Prestressed Concrete Girder</v>
+      </c>
+      <c r="R17">
+        <v>1972</v>
+      </c>
+      <c r="S17" t="str">
+        <v>T44</v>
+      </c>
+      <c r="T17" t="str">
+        <v>AS5100</v>
+      </c>
+      <c r="U17">
+        <v>9</v>
+      </c>
+      <c r="V17">
+        <v>30</v>
+      </c>
+      <c r="W17" t="str">
+        <v>Concrete</v>
+      </c>
+      <c r="X17">
+        <v>8</v>
+      </c>
+      <c r="Y17">
+        <v>256</v>
+      </c>
+      <c r="Z17">
+        <v>11.4</v>
+      </c>
+      <c r="AA17">
+        <v>2</v>
+      </c>
+      <c r="AB17" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC17">
+        <v>3</v>
+      </c>
+      <c r="AD17">
+        <v>6</v>
+      </c>
+      <c r="AE17" t="str">
+        <v>Unrestricted</v>
+      </c>
+      <c r="AF17" t="str">
+        <v>AS 5100.7</v>
+      </c>
+      <c r="AG17" t="str">
+        <v>Zone 1</v>
+      </c>
+      <c r="AH17" t="str">
+        <v/>
+      </c>
+      <c r="AI17" t="str">
+        <v/>
+      </c>
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="str">
+        <v>Primary east-west freight crossing. High percentage heavy vehicles due to agricultural freight.</v>
+      </c>
+      <c r="AM17" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN17" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="AO17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="AQ17">
+        <v>35</v>
+      </c>
+      <c r="AR17" t="str">
+        <v/>
+      </c>
+      <c r="AS17" t="str">
+        <v/>
+      </c>
+      <c r="AT17">
+        <v>11200</v>
+      </c>
+      <c r="AU17">
+        <v>28</v>
+      </c>
+      <c r="AV17" t="str">
+        <v/>
+      </c>
+      <c r="AW17" t="str">
+        <v/>
+      </c>
+      <c r="AX17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ17" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA17" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB17" t="str">
         <v>DEMO</v>
       </c>
-      <c r="BD16" t="str">
-        <v/>
-      </c>
-      <c r="BE16" t="str">
-        <v/>
-      </c>
-      <c r="BF16" t="str">
-        <v/>
-      </c>
-      <c r="BG16" t="str">
-        <v/>
-      </c>
-      <c r="BH16" t="str">
-        <v>{"type":"LineString","coordinates":[[152.996,-30.492],[153.003,-30.492]]}</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>1016</v>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v>BRG-NSW-NEW-001</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Macquarie River Bridge (Dubbo)</v>
-      </c>
-      <c r="E17" t="str">
+      <c r="BC17" t="str">
+        <v/>
+      </c>
+      <c r="BD17" t="str">
+        <v/>
+      </c>
+      <c r="BE17" t="str">
+        <v/>
+      </c>
+      <c r="BF17" t="str">
+        <v/>
+      </c>
+      <c r="BG17" t="str">
+        <v>{"type":"LineString","coordinates":[[148.509,-32.297],[148.516,-32.297]]}</v>
+      </c>
+      <c r="BH17" t="str">
+        <v/>
+      </c>
+      <c r="BI17" t="str">
+        <v/>
+      </c>
+      <c r="BJ17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>BRG-NSW-NEW-002</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Cooradah River Bridge</v>
+      </c>
+      <c r="F18" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F17" t="str">
-        <v>Cobra Street</v>
-      </c>
-      <c r="G17" t="str">
-        <v>B54</v>
-      </c>
-      <c r="H17" t="str">
+      <c r="G18" t="str">
+        <v>Inland Highway</v>
+      </c>
+      <c r="H18" t="str">
+        <v>A39</v>
+      </c>
+      <c r="I18" t="str">
         <v>NSW</v>
       </c>
-      <c r="I17" t="str">
+      <c r="J18" t="str">
         <v>Western NSW</v>
       </c>
-      <c r="J17" t="str">
-        <v>Dubbo Regional</v>
-      </c>
-      <c r="K17" t="str">
-        <v>-32.239400</v>
-      </c>
-      <c r="L17" t="str">
-        <v>148.588600</v>
-      </c>
-      <c r="M17" t="str">
-        <v>Macquarie River</v>
-      </c>
-      <c r="N17" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O17" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P17" t="str">
+      <c r="K18" t="str">
+        <v>Cooradah</v>
+      </c>
+      <c r="L18">
+        <v>-30.3842</v>
+      </c>
+      <c r="M18">
+        <v>149.7126</v>
+      </c>
+      <c r="N18" t="str">
+        <v>Cooradah River</v>
+      </c>
+      <c r="O18" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P18" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q18" t="str">
         <v>Prestressed Concrete Girder</v>
       </c>
-      <c r="Q17">
-        <v>1972</v>
-      </c>
-      <c r="R17" t="str">
+      <c r="R18">
+        <v>1985</v>
+      </c>
+      <c r="S18" t="str">
         <v>T44</v>
       </c>
-      <c r="S17" t="str">
+      <c r="T18" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T17" t="str">
-        <v>9.00</v>
-      </c>
-      <c r="U17" t="str">
-        <v>30.00</v>
-      </c>
-      <c r="V17" t="str">
+      <c r="U18">
+        <v>10.2</v>
+      </c>
+      <c r="V18">
+        <v>34</v>
+      </c>
+      <c r="W18" t="str">
         <v>Concrete</v>
       </c>
-      <c r="W17">
-        <v>8</v>
-      </c>
-      <c r="X17" t="str">
-        <v>256.00</v>
-      </c>
-      <c r="Y17" t="str">
-        <v>11.40</v>
-      </c>
-      <c r="Z17">
+      <c r="X18">
+        <v>7</v>
+      </c>
+      <c r="Y18">
+        <v>248</v>
+      </c>
+      <c r="Z18">
+        <v>12</v>
+      </c>
+      <c r="AA18">
         <v>2</v>
       </c>
-      <c r="AA17" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB17">
-        <v>5</v>
-      </c>
-      <c r="AC17">
-        <v>6</v>
-      </c>
-      <c r="AD17" t="str">
+      <c r="AB18" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC18">
+        <v>2</v>
+      </c>
+      <c r="AD18">
+        <v>7</v>
+      </c>
+      <c r="AE18" t="str">
         <v>Unrestricted</v>
       </c>
-      <c r="AE17" t="str">
+      <c r="AF18" t="str">
+        <v>AS 5100</v>
+      </c>
+      <c r="AG18" t="str">
+        <v>Zone 1</v>
+      </c>
+      <c r="AH18" t="str">
+        <v/>
+      </c>
+      <c r="AI18" t="str">
+        <v/>
+      </c>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="str">
+        <v>Major inland freight highway crossing. High agricultural freight use — cotton and grain season peaks.</v>
+      </c>
+      <c r="AM18" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN18" t="str">
+        <v>2025-10-14</v>
+      </c>
+      <c r="AO18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP18" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="AQ18">
+        <v>37.5</v>
+      </c>
+      <c r="AR18" t="str">
+        <v/>
+      </c>
+      <c r="AS18" t="str">
+        <v/>
+      </c>
+      <c r="AT18">
+        <v>7600</v>
+      </c>
+      <c r="AU18">
+        <v>32</v>
+      </c>
+      <c r="AV18" t="str">
+        <v/>
+      </c>
+      <c r="AW18" t="str">
+        <v/>
+      </c>
+      <c r="AX18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB18" t="str">
+        <v>DEMO</v>
+      </c>
+      <c r="BC18" t="str">
+        <v/>
+      </c>
+      <c r="BD18" t="str">
+        <v/>
+      </c>
+      <c r="BE18" t="str">
+        <v/>
+      </c>
+      <c r="BF18" t="str">
+        <v/>
+      </c>
+      <c r="BG18" t="str">
+        <v>{"type":"LineString","coordinates":[[149.710,-30.384],[149.716,-30.384]]}</v>
+      </c>
+      <c r="BH18" t="str">
+        <v/>
+      </c>
+      <c r="BI18" t="str">
+        <v/>
+      </c>
+      <c r="BJ18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>BRG-NSW-NEW-003</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Pendleton River Bridge</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Road Bridge</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Highlands Highway</v>
+      </c>
+      <c r="H19" t="str">
+        <v>A15</v>
+      </c>
+      <c r="I19" t="str">
+        <v>NSW</v>
+      </c>
+      <c r="J19" t="str">
+        <v>New England</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Pendleton Regional</v>
+      </c>
+      <c r="L19">
+        <v>-31.1424</v>
+      </c>
+      <c r="M19">
+        <v>150.8642</v>
+      </c>
+      <c r="N19" t="str">
+        <v>Pendleton River</v>
+      </c>
+      <c r="O19" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P19" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>Truss Bridge</v>
+      </c>
+      <c r="R19">
+        <v>1958</v>
+      </c>
+      <c r="S19" t="str">
+        <v>T44</v>
+      </c>
+      <c r="T19" t="str">
+        <v>AS5100</v>
+      </c>
+      <c r="U19">
+        <v>7.8</v>
+      </c>
+      <c r="V19">
+        <v>62</v>
+      </c>
+      <c r="W19" t="str">
+        <v>Steel</v>
+      </c>
+      <c r="X19">
+        <v>3</v>
+      </c>
+      <c r="Y19">
+        <v>199</v>
+      </c>
+      <c r="Z19">
+        <v>9.6</v>
+      </c>
+      <c r="AA19">
+        <v>2</v>
+      </c>
+      <c r="AB19" t="str">
+        <v>4</v>
+      </c>
+      <c r="AC19">
+        <v>4</v>
+      </c>
+      <c r="AD19">
+        <v>3</v>
+      </c>
+      <c r="AE19" t="str">
+        <v>Restricted</v>
+      </c>
+      <c r="AF19" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF17" t="str">
+      <c r="AG19" t="str">
         <v>Zone 1</v>
       </c>
-      <c r="AG17" t="str">
-        <v/>
-      </c>
-      <c r="AH17" t="str">
-        <v/>
-      </c>
-      <c r="AI17" t="str">
-        <v/>
-      </c>
-      <c r="AJ17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="str">
-        <v>Primary east-west freight crossing at Dubbo. High percentage heavy vehicles due to agricultural freight.</v>
-      </c>
-      <c r="AM17" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN17" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO17" t="str">
-        <v>2025-09-03</v>
-      </c>
-      <c r="AP17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ17" t="str">
-        <v>2025-09-08</v>
-      </c>
-      <c r="AR17" t="str">
-        <v>35.00</v>
-      </c>
-      <c r="AS17" t="str">
-        <v/>
-      </c>
-      <c r="AT17" t="str">
-        <v/>
-      </c>
-      <c r="AU17">
-        <v>11200</v>
-      </c>
-      <c r="AV17" t="str">
-        <v>28.00</v>
-      </c>
-      <c r="AW17" t="str">
-        <v/>
-      </c>
-      <c r="AX17" t="str">
-        <v/>
-      </c>
-      <c r="AY17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ17" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA17" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB17" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC17" t="str">
+      <c r="AH19" t="str">
+        <v/>
+      </c>
+      <c r="AI19" t="str">
+        <v/>
+      </c>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="str">
+        <v>67-year-old truss structure. GML 19t restricts B-double access on the highlands corridor. Replacement funding sought.</v>
+      </c>
+      <c r="AM19" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN19" t="str">
+        <v>2025-04-22</v>
+      </c>
+      <c r="AO19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="str">
+        <v/>
+      </c>
+      <c r="AQ19">
+        <v>19</v>
+      </c>
+      <c r="AR19" t="str">
+        <v/>
+      </c>
+      <c r="AS19" t="str">
+        <v/>
+      </c>
+      <c r="AT19">
+        <v>9200</v>
+      </c>
+      <c r="AU19">
+        <v>22</v>
+      </c>
+      <c r="AV19" t="str">
+        <v/>
+      </c>
+      <c r="AW19" t="str">
+        <v/>
+      </c>
+      <c r="AX19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="str">
         <v>DEMO</v>
       </c>
-      <c r="BD17" t="str">
-        <v/>
-      </c>
-      <c r="BE17" t="str">
-        <v/>
-      </c>
-      <c r="BF17" t="str">
-        <v/>
-      </c>
-      <c r="BG17" t="str">
-        <v/>
-      </c>
-      <c r="BH17" t="str">
-        <v>{"type":"LineString","coordinates":[[148.585,-32.239],[148.592,-32.239]]}</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>1017</v>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v>BRG-NSW-NEW-002</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Namoi River Bridge (Narrabri)</v>
-      </c>
-      <c r="E18" t="str">
+      <c r="BC19" t="str">
+        <v/>
+      </c>
+      <c r="BD19" t="str">
+        <v/>
+      </c>
+      <c r="BE19" t="str">
+        <v/>
+      </c>
+      <c r="BF19" t="str">
+        <v/>
+      </c>
+      <c r="BG19" t="str">
+        <v>{"type":"LineString","coordinates":[[150.861,-31.142],[150.868,-31.142]]}</v>
+      </c>
+      <c r="BH19" t="str">
+        <v/>
+      </c>
+      <c r="BI19" t="str">
+        <v/>
+      </c>
+      <c r="BJ19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v/>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>BRG-NSW-ILL-001</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Saltwater River Bridge</v>
+      </c>
+      <c r="F20" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F18" t="str">
-        <v>Newell Highway</v>
-      </c>
-      <c r="G18" t="str">
-        <v>A39</v>
-      </c>
-      <c r="H18" t="str">
+      <c r="G20" t="str">
+        <v>South Coast Highway</v>
+      </c>
+      <c r="H20" t="str">
+        <v>A1</v>
+      </c>
+      <c r="I20" t="str">
         <v>NSW</v>
       </c>
-      <c r="I18" t="str">
-        <v>Western NSW</v>
-      </c>
-      <c r="J18" t="str">
-        <v>Narrabri</v>
-      </c>
-      <c r="K18" t="str">
-        <v>-30.330100</v>
-      </c>
-      <c r="L18" t="str">
-        <v>149.776400</v>
-      </c>
-      <c r="M18" t="str">
-        <v>Namoi River</v>
-      </c>
-      <c r="N18" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O18" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P18" t="str">
-        <v>Prestressed Concrete Girder</v>
-      </c>
-      <c r="Q18">
-        <v>1985</v>
-      </c>
-      <c r="R18" t="str">
+      <c r="J20" t="str">
+        <v>Southern NSW</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Saltwater</v>
+      </c>
+      <c r="L20">
+        <v>-34.9126</v>
+      </c>
+      <c r="M20">
+        <v>150.5482</v>
+      </c>
+      <c r="N20" t="str">
+        <v>Saltwater River</v>
+      </c>
+      <c r="O20" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P20" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>Arch Truss Bridge</v>
+      </c>
+      <c r="R20">
+        <v>1881</v>
+      </c>
+      <c r="S20" t="str">
         <v>T44</v>
       </c>
-      <c r="S18" t="str">
+      <c r="T20" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T18" t="str">
-        <v>10.20</v>
-      </c>
-      <c r="U18" t="str">
-        <v>34.00</v>
-      </c>
-      <c r="V18" t="str">
-        <v>Concrete</v>
-      </c>
-      <c r="W18">
-        <v>7</v>
-      </c>
-      <c r="X18" t="str">
-        <v>248.00</v>
-      </c>
-      <c r="Y18" t="str">
-        <v>12.00</v>
-      </c>
-      <c r="Z18">
+      <c r="U20">
+        <v>11</v>
+      </c>
+      <c r="V20">
+        <v>88</v>
+      </c>
+      <c r="W20" t="str">
+        <v>Steel</v>
+      </c>
+      <c r="X20">
+        <v>4</v>
+      </c>
+      <c r="Y20">
+        <v>387</v>
+      </c>
+      <c r="Z20">
+        <v>9.2</v>
+      </c>
+      <c r="AA20">
         <v>2</v>
       </c>
-      <c r="AA18" t="str">
-        <v>Good</v>
-      </c>
-      <c r="AB18">
-        <v>7</v>
-      </c>
-      <c r="AC18">
-        <v>7</v>
-      </c>
-      <c r="AD18" t="str">
+      <c r="AB20" t="str">
+        <v>4</v>
+      </c>
+      <c r="AC20">
+        <v>4</v>
+      </c>
+      <c r="AD20">
+        <v>3</v>
+      </c>
+      <c r="AE20" t="str">
+        <v>Restricted</v>
+      </c>
+      <c r="AF20" t="str">
+        <v>AS 5100.7</v>
+      </c>
+      <c r="AG20" t="str">
+        <v>Zone 1</v>
+      </c>
+      <c r="AH20" t="str">
+        <v/>
+      </c>
+      <c r="AI20" t="str">
+        <v/>
+      </c>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="str">
+        <v>Heritage listed 143-year-old wrought iron truss. GML 16t. Critical south coast bottleneck. Replacement under construction (2026 target).</v>
+      </c>
+      <c r="AM20" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN20" t="str">
+        <v>2025-03-17</v>
+      </c>
+      <c r="AO20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="str">
+        <v/>
+      </c>
+      <c r="AQ20">
+        <v>16</v>
+      </c>
+      <c r="AR20" t="str">
+        <v/>
+      </c>
+      <c r="AS20" t="str">
+        <v/>
+      </c>
+      <c r="AT20">
+        <v>28000</v>
+      </c>
+      <c r="AU20">
+        <v>15</v>
+      </c>
+      <c r="AV20" t="str">
+        <v/>
+      </c>
+      <c r="AW20" t="str">
+        <v/>
+      </c>
+      <c r="AX20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="str">
+        <v>DEMO</v>
+      </c>
+      <c r="BC20" t="str">
+        <v/>
+      </c>
+      <c r="BD20" t="str">
+        <v/>
+      </c>
+      <c r="BE20" t="str">
+        <v/>
+      </c>
+      <c r="BF20" t="str">
+        <v/>
+      </c>
+      <c r="BG20" t="str">
+        <v>{"type":"LineString","coordinates":[[150.545,-34.913],[150.552,-34.913]]}</v>
+      </c>
+      <c r="BH20" t="str">
+        <v/>
+      </c>
+      <c r="BI20" t="str">
+        <v/>
+      </c>
+      <c r="BJ20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v/>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>BRG-NSW-ILL-002</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Oyster Bay Bridge</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Road Bridge</v>
+      </c>
+      <c r="G21" t="str">
+        <v>South Coast Highway</v>
+      </c>
+      <c r="H21" t="str">
+        <v>A1</v>
+      </c>
+      <c r="I21" t="str">
+        <v>NSW</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Southern NSW</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Oyster Bay</v>
+      </c>
+      <c r="L21">
+        <v>-35.7486</v>
+      </c>
+      <c r="M21">
+        <v>150.1248</v>
+      </c>
+      <c r="N21" t="str">
+        <v>Oyster River</v>
+      </c>
+      <c r="O21" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P21" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>Cable-stayed Bridge</v>
+      </c>
+      <c r="R21">
+        <v>2023</v>
+      </c>
+      <c r="S21" t="str">
+        <v>SM1600</v>
+      </c>
+      <c r="T21" t="str">
+        <v>AS5100</v>
+      </c>
+      <c r="U21">
+        <v>20</v>
+      </c>
+      <c r="V21">
+        <v>200</v>
+      </c>
+      <c r="W21" t="str">
+        <v>Concrete and Steel</v>
+      </c>
+      <c r="X21">
+        <v>3</v>
+      </c>
+      <c r="Y21">
+        <v>425</v>
+      </c>
+      <c r="Z21">
+        <v>16.8</v>
+      </c>
+      <c r="AA21">
+        <v>4</v>
+      </c>
+      <c r="AB21" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AD21">
+        <v>10</v>
+      </c>
+      <c r="AE21" t="str">
         <v>Unrestricted</v>
       </c>
-      <c r="AE18" t="str">
+      <c r="AF21" t="str">
         <v>AS 5100</v>
       </c>
-      <c r="AF18" t="str">
+      <c r="AG21" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG18" t="str">
-        <v/>
-      </c>
-      <c r="AH18" t="str">
-        <v/>
-      </c>
-      <c r="AI18" t="str">
-        <v/>
-      </c>
-      <c r="AJ18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="str">
-        <v>Newell Highway is Australia's longest inland highway. High agricultural freight use — cotton and grain season peaks.</v>
-      </c>
-      <c r="AM18" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN18" t="str">
-        <v>Low</v>
-      </c>
-      <c r="AO18" t="str">
-        <v>2025-10-14</v>
-      </c>
-      <c r="AP18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ18" t="str">
-        <v>2025-10-20</v>
-      </c>
-      <c r="AR18" t="str">
-        <v>37.50</v>
-      </c>
-      <c r="AS18" t="str">
-        <v/>
-      </c>
-      <c r="AT18" t="str">
-        <v/>
-      </c>
-      <c r="AU18">
-        <v>7600</v>
-      </c>
-      <c r="AV18" t="str">
-        <v>32.00</v>
-      </c>
-      <c r="AW18" t="str">
-        <v/>
-      </c>
-      <c r="AX18" t="str">
-        <v/>
-      </c>
-      <c r="AY18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ18" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA18" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB18" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC18" t="str">
-        <v>DEMO</v>
-      </c>
-      <c r="BD18" t="str">
-        <v/>
-      </c>
-      <c r="BE18" t="str">
-        <v/>
-      </c>
-      <c r="BF18" t="str">
-        <v/>
-      </c>
-      <c r="BG18" t="str">
-        <v/>
-      </c>
-      <c r="BH18" t="str">
-        <v>{"type":"LineString","coordinates":[[149.773,-30.330],[149.780,-30.330]]}</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>1018</v>
-      </c>
-      <c r="B19" t="str">
-        <v/>
-      </c>
-      <c r="C19" t="str">
-        <v>BRG-NSW-NEW-003</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Peel River Bridge (Tamworth)</v>
-      </c>
-      <c r="E19" t="str">
-        <v>Road Bridge</v>
-      </c>
-      <c r="F19" t="str">
-        <v>New England Highway</v>
-      </c>
-      <c r="G19" t="str">
-        <v>A15</v>
-      </c>
-      <c r="H19" t="str">
-        <v>NSW</v>
-      </c>
-      <c r="I19" t="str">
-        <v>New England</v>
-      </c>
-      <c r="J19" t="str">
-        <v>Tamworth Regional</v>
-      </c>
-      <c r="K19" t="str">
-        <v>-31.088800</v>
-      </c>
-      <c r="L19" t="str">
-        <v>150.918500</v>
-      </c>
-      <c r="M19" t="str">
-        <v>Peel River</v>
-      </c>
-      <c r="N19" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O19" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P19" t="str">
-        <v>Truss Bridge</v>
-      </c>
-      <c r="Q19">
-        <v>1958</v>
-      </c>
-      <c r="R19" t="str">
-        <v>T44</v>
-      </c>
-      <c r="S19" t="str">
-        <v>AS5100</v>
-      </c>
-      <c r="T19" t="str">
-        <v>7.80</v>
-      </c>
-      <c r="U19" t="str">
-        <v>62.00</v>
-      </c>
-      <c r="V19" t="str">
-        <v>Steel</v>
-      </c>
-      <c r="W19">
-        <v>3</v>
-      </c>
-      <c r="X19" t="str">
-        <v>199.00</v>
-      </c>
-      <c r="Y19" t="str">
-        <v>9.60</v>
-      </c>
-      <c r="Z19">
-        <v>2</v>
-      </c>
-      <c r="AA19" t="str">
-        <v>Poor</v>
-      </c>
-      <c r="AB19">
-        <v>3</v>
-      </c>
-      <c r="AC19">
-        <v>3</v>
-      </c>
-      <c r="AD19" t="str">
-        <v>Restricted</v>
-      </c>
-      <c r="AE19" t="str">
-        <v>AS 5100.7</v>
-      </c>
-      <c r="AF19" t="str">
-        <v>Zone 1</v>
-      </c>
-      <c r="AG19" t="str">
-        <v/>
-      </c>
-      <c r="AH19" t="str">
-        <v/>
-      </c>
-      <c r="AI19" t="str">
-        <v/>
-      </c>
-      <c r="AJ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="str">
-        <v>67-year-old truss structure. GML 19t restricts B-double access on New England Highway. Replacement funding sought.</v>
-      </c>
-      <c r="AM19" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN19" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO19" t="str">
-        <v>2025-04-22</v>
-      </c>
-      <c r="AP19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="str">
-        <v/>
-      </c>
-      <c r="AR19" t="str">
-        <v>19.00</v>
-      </c>
-      <c r="AS19" t="str">
-        <v/>
-      </c>
-      <c r="AT19" t="str">
-        <v/>
-      </c>
-      <c r="AU19">
-        <v>9200</v>
-      </c>
-      <c r="AV19" t="str">
-        <v>22.00</v>
-      </c>
-      <c r="AW19" t="str">
-        <v/>
-      </c>
-      <c r="AX19" t="str">
-        <v/>
-      </c>
-      <c r="AY19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="str">
-        <v>DEMO</v>
-      </c>
-      <c r="BD19" t="str">
-        <v/>
-      </c>
-      <c r="BE19" t="str">
-        <v/>
-      </c>
-      <c r="BF19" t="str">
-        <v/>
-      </c>
-      <c r="BG19" t="str">
-        <v/>
-      </c>
-      <c r="BH19" t="str">
-        <v>{"type":"LineString","coordinates":[[150.915,-31.089],[150.922,-31.089]]}</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>1019</v>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v>BRG-NSW-ILL-001</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Shoalhaven River Bridge (Nowra)</v>
-      </c>
-      <c r="E20" t="str">
-        <v>Road Bridge</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Princes Highway</v>
-      </c>
-      <c r="G20" t="str">
-        <v>A1</v>
-      </c>
-      <c r="H20" t="str">
-        <v>NSW</v>
-      </c>
-      <c r="I20" t="str">
-        <v>Southern NSW</v>
-      </c>
-      <c r="J20" t="str">
-        <v>Shoalhaven</v>
-      </c>
-      <c r="K20" t="str">
-        <v>-34.871200</v>
-      </c>
-      <c r="L20" t="str">
-        <v>150.597400</v>
-      </c>
-      <c r="M20" t="str">
-        <v>Shoalhaven River</v>
-      </c>
-      <c r="N20" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O20" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P20" t="str">
-        <v>Arch Truss Bridge</v>
-      </c>
-      <c r="Q20">
-        <v>1881</v>
-      </c>
-      <c r="R20" t="str">
-        <v>T44</v>
-      </c>
-      <c r="S20" t="str">
-        <v>AS5100</v>
-      </c>
-      <c r="T20" t="str">
-        <v>11.00</v>
-      </c>
-      <c r="U20" t="str">
-        <v>88.00</v>
-      </c>
-      <c r="V20" t="str">
-        <v>Steel</v>
-      </c>
-      <c r="W20">
-        <v>4</v>
-      </c>
-      <c r="X20" t="str">
-        <v>387.00</v>
-      </c>
-      <c r="Y20" t="str">
-        <v>9.20</v>
-      </c>
-      <c r="Z20">
-        <v>2</v>
-      </c>
-      <c r="AA20" t="str">
-        <v>Poor</v>
-      </c>
-      <c r="AB20">
-        <v>3</v>
-      </c>
-      <c r="AC20">
-        <v>3</v>
-      </c>
-      <c r="AD20" t="str">
-        <v>Restricted</v>
-      </c>
-      <c r="AE20" t="str">
-        <v>AS 5100.7</v>
-      </c>
-      <c r="AF20" t="str">
-        <v>Zone 1</v>
-      </c>
-      <c r="AG20" t="str">
-        <v/>
-      </c>
-      <c r="AH20" t="str">
-        <v/>
-      </c>
-      <c r="AI20" t="str">
-        <v/>
-      </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="str">
-        <v>Heritage listed 143-year-old wrought iron truss. GML 16t. Critical Princes Highway bottleneck. Replacement under construction (2026 target).</v>
-      </c>
-      <c r="AM20" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN20" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO20" t="str">
-        <v>2025-03-17</v>
-      </c>
-      <c r="AP20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="str">
-        <v/>
-      </c>
-      <c r="AR20" t="str">
-        <v>16.00</v>
-      </c>
-      <c r="AS20" t="str">
-        <v/>
-      </c>
-      <c r="AT20" t="str">
-        <v/>
-      </c>
-      <c r="AU20">
-        <v>28000</v>
-      </c>
-      <c r="AV20" t="str">
-        <v>15.00</v>
-      </c>
-      <c r="AW20" t="str">
-        <v/>
-      </c>
-      <c r="AX20" t="str">
-        <v/>
-      </c>
-      <c r="AY20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="str">
-        <v>DEMO</v>
-      </c>
-      <c r="BD20" t="str">
-        <v/>
-      </c>
-      <c r="BE20" t="str">
-        <v/>
-      </c>
-      <c r="BF20" t="str">
-        <v/>
-      </c>
-      <c r="BG20" t="str">
-        <v/>
-      </c>
-      <c r="BH20" t="str">
-        <v>{"type":"LineString","coordinates":[[150.594,-34.871],[150.601,-34.871]]}</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>1020</v>
-      </c>
-      <c r="B21" t="str">
-        <v/>
-      </c>
-      <c r="C21" t="str">
-        <v>BRG-NSW-ILL-002</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Clyde River Bridge (Batemans Bay)</v>
-      </c>
-      <c r="E21" t="str">
-        <v>Road Bridge</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Princes Highway</v>
-      </c>
-      <c r="G21" t="str">
-        <v>A1</v>
-      </c>
-      <c r="H21" t="str">
-        <v>NSW</v>
-      </c>
-      <c r="I21" t="str">
-        <v>Southern NSW</v>
-      </c>
-      <c r="J21" t="str">
-        <v>Eurobodalla</v>
-      </c>
-      <c r="K21" t="str">
-        <v>-35.707300</v>
-      </c>
-      <c r="L21" t="str">
-        <v>150.174600</v>
-      </c>
-      <c r="M21" t="str">
-        <v>Clyde River</v>
-      </c>
-      <c r="N21" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O21" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P21" t="str">
-        <v>Cable-stayed Bridge</v>
-      </c>
-      <c r="Q21">
-        <v>2023</v>
-      </c>
-      <c r="R21" t="str">
-        <v>SM1600</v>
-      </c>
-      <c r="S21" t="str">
-        <v>AS5100</v>
-      </c>
-      <c r="T21" t="str">
-        <v>20.00</v>
-      </c>
-      <c r="U21" t="str">
-        <v>200.00</v>
-      </c>
-      <c r="V21" t="str">
-        <v>Concrete and Steel</v>
-      </c>
-      <c r="W21">
-        <v>3</v>
-      </c>
-      <c r="X21" t="str">
-        <v>425.00</v>
-      </c>
-      <c r="Y21" t="str">
-        <v>16.80</v>
-      </c>
-      <c r="Z21">
-        <v>4</v>
-      </c>
-      <c r="AA21" t="str">
-        <v>Excellent</v>
-      </c>
-      <c r="AB21">
-        <v>10</v>
-      </c>
-      <c r="AC21">
-        <v>10</v>
-      </c>
-      <c r="AD21" t="str">
-        <v>Unrestricted</v>
-      </c>
-      <c r="AE21" t="str">
-        <v>AS 5100</v>
-      </c>
-      <c r="AF21" t="str">
-        <v>Zone 1</v>
-      </c>
-      <c r="AG21" t="str">
-        <v/>
       </c>
       <c r="AH21" t="str">
         <v/>
@@ -5376,40 +5489,40 @@
         <v>Brand new 2023 bridge replacing the 1956 structure. 4-lane dual carriageway. Designed for bushfire and flood resilience.</v>
       </c>
       <c r="AM21" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN21" t="str">
-        <v>Low</v>
-      </c>
-      <c r="AO21" t="str">
         <v>2025-11-10</v>
       </c>
-      <c r="AP21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ21" t="str">
+      <c r="AO21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="str">
         <v>2025-11-15</v>
       </c>
+      <c r="AQ21">
+        <v>50</v>
+      </c>
       <c r="AR21" t="str">
-        <v>50.00</v>
+        <v/>
       </c>
       <c r="AS21" t="str">
         <v/>
       </c>
-      <c r="AT21" t="str">
-        <v/>
+      <c r="AT21">
+        <v>18500</v>
       </c>
       <c r="AU21">
-        <v>18500</v>
+        <v>14</v>
       </c>
       <c r="AV21" t="str">
-        <v>14.00</v>
+        <v/>
       </c>
       <c r="AW21" t="str">
         <v/>
       </c>
-      <c r="AX21" t="str">
-        <v/>
+      <c r="AX21" t="b">
+        <v>1</v>
       </c>
       <c r="AY21" t="b">
         <v>1</v>
@@ -5420,11 +5533,11 @@
       <c r="BA21" t="b">
         <v>1</v>
       </c>
-      <c r="BB21" t="b">
-        <v>1</v>
+      <c r="BB21" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC21" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD21" t="str">
         <v/>
@@ -5436,111 +5549,117 @@
         <v/>
       </c>
       <c r="BG21" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[150.122,-35.749],[150.128,-35.749]]}</v>
       </c>
       <c r="BH21" t="str">
-        <v>{"type":"LineString","coordinates":[[150.171,-35.707],[150.178,-35.707]]}</v>
+        <v/>
+      </c>
+      <c r="BI21" t="str">
+        <v/>
+      </c>
+      <c r="BJ21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>1021</v>
+      <c r="A22" t="str">
+        <v/>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
         <v>BRG-NSW-ILL-003</v>
       </c>
-      <c r="D22" t="str">
-        <v>Moruya River Bridge</v>
-      </c>
       <c r="E22" t="str">
+        <v>Merrindale River Bridge</v>
+      </c>
+      <c r="F22" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F22" t="str">
-        <v>Princes Highway</v>
-      </c>
       <c r="G22" t="str">
+        <v>South Coast Highway</v>
+      </c>
+      <c r="H22" t="str">
         <v>A1</v>
       </c>
-      <c r="H22" t="str">
+      <c r="I22" t="str">
         <v>NSW</v>
       </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
         <v>Southern NSW</v>
       </c>
-      <c r="J22" t="str">
-        <v>Eurobodalla</v>
-      </c>
       <c r="K22" t="str">
-        <v>-35.904600</v>
-      </c>
-      <c r="L22" t="str">
-        <v>150.076300</v>
-      </c>
-      <c r="M22" t="str">
-        <v>Moruya River</v>
+        <v>Oyster Bay</v>
+      </c>
+      <c r="L22">
+        <v>-35.9482</v>
+      </c>
+      <c r="M22">
+        <v>150.0246</v>
       </c>
       <c r="N22" t="str">
-        <v>Transport for NSW</v>
+        <v>Merrindale River</v>
       </c>
       <c r="O22" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="P22" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q22" t="str">
         <v>Prestressed Concrete Girder</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>1977</v>
       </c>
-      <c r="R22" t="str">
+      <c r="S22" t="str">
         <v>T44</v>
       </c>
-      <c r="S22" t="str">
+      <c r="T22" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T22" t="str">
-        <v>7.60</v>
-      </c>
-      <c r="U22" t="str">
-        <v>30.00</v>
-      </c>
-      <c r="V22" t="str">
+      <c r="U22">
+        <v>7.6</v>
+      </c>
+      <c r="V22">
+        <v>30</v>
+      </c>
+      <c r="W22" t="str">
         <v>Concrete</v>
       </c>
-      <c r="W22">
+      <c r="X22">
         <v>6</v>
       </c>
-      <c r="X22" t="str">
-        <v>194.00</v>
-      </c>
-      <c r="Y22" t="str">
-        <v>11.00</v>
+      <c r="Y22">
+        <v>194</v>
       </c>
       <c r="Z22">
+        <v>11</v>
+      </c>
+      <c r="AA22">
         <v>2</v>
       </c>
-      <c r="AA22" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB22">
+      <c r="AB22" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC22">
+        <v>3</v>
+      </c>
+      <c r="AD22">
         <v>6</v>
       </c>
-      <c r="AC22">
-        <v>6</v>
-      </c>
-      <c r="AD22" t="str">
+      <c r="AE22" t="str">
         <v>Unrestricted</v>
       </c>
-      <c r="AE22" t="str">
+      <c r="AF22" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF22" t="str">
+      <c r="AG22" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG22" t="str">
-        <v/>
       </c>
       <c r="AH22" t="str">
         <v/>
@@ -5558,55 +5677,55 @@
         <v>South coast highway bridge. Minor scour observed at Pier 3 — monitoring programme established 2023.</v>
       </c>
       <c r="AM22" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN22" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO22" t="str">
         <v>2025-08-28</v>
       </c>
-      <c r="AP22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ22" t="str">
+      <c r="AO22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="str">
         <v>2025-09-03</v>
       </c>
+      <c r="AQ22">
+        <v>34.5</v>
+      </c>
       <c r="AR22" t="str">
-        <v>34.50</v>
+        <v/>
       </c>
       <c r="AS22" t="str">
         <v/>
       </c>
-      <c r="AT22" t="str">
-        <v/>
+      <c r="AT22">
+        <v>6400</v>
       </c>
       <c r="AU22">
-        <v>6400</v>
+        <v>12</v>
       </c>
       <c r="AV22" t="str">
-        <v>12.00</v>
+        <v/>
       </c>
       <c r="AW22" t="str">
         <v/>
       </c>
-      <c r="AX22" t="str">
-        <v/>
+      <c r="AX22" t="b">
+        <v>1</v>
       </c>
       <c r="AY22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA22" t="b">
         <v>1</v>
       </c>
-      <c r="BB22" t="b">
-        <v>1</v>
+      <c r="BB22" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC22" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD22" t="str">
         <v/>
@@ -5618,111 +5737,117 @@
         <v/>
       </c>
       <c r="BG22" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[150.022,-35.948],[150.028,-35.948]]}</v>
       </c>
       <c r="BH22" t="str">
-        <v>{"type":"LineString","coordinates":[[150.073,-35.905],[150.080,-35.905]]}</v>
+        <v/>
+      </c>
+      <c r="BI22" t="str">
+        <v/>
+      </c>
+      <c r="BJ22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>1022</v>
+      <c r="A23" t="str">
+        <v/>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
         <v>BRG-NSW-ILL-004</v>
       </c>
-      <c r="D23" t="str">
-        <v>Bega River Bridge</v>
-      </c>
       <c r="E23" t="str">
+        <v>Silverwood River Bridge</v>
+      </c>
+      <c r="F23" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F23" t="str">
-        <v>Princes Highway</v>
-      </c>
       <c r="G23" t="str">
+        <v>South Coast Highway</v>
+      </c>
+      <c r="H23" t="str">
         <v>A1</v>
       </c>
-      <c r="H23" t="str">
+      <c r="I23" t="str">
         <v>NSW</v>
       </c>
-      <c r="I23" t="str">
+      <c r="J23" t="str">
         <v>Southern NSW</v>
       </c>
-      <c r="J23" t="str">
-        <v>Bega Valley</v>
-      </c>
       <c r="K23" t="str">
-        <v>-36.676200</v>
-      </c>
-      <c r="L23" t="str">
-        <v>149.837000</v>
-      </c>
-      <c r="M23" t="str">
-        <v>Bega River</v>
+        <v>Silverwood Valley</v>
+      </c>
+      <c r="L23">
+        <v>-36.7124</v>
+      </c>
+      <c r="M23">
+        <v>149.7986</v>
       </c>
       <c r="N23" t="str">
-        <v>Transport for NSW</v>
+        <v>Silverwood River</v>
       </c>
       <c r="O23" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="P23" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q23" t="str">
         <v>Prestressed Concrete Girder</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>1969</v>
       </c>
-      <c r="R23" t="str">
+      <c r="S23" t="str">
         <v>T44</v>
       </c>
-      <c r="S23" t="str">
+      <c r="T23" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T23" t="str">
-        <v>7.00</v>
-      </c>
-      <c r="U23" t="str">
-        <v>28.00</v>
-      </c>
-      <c r="V23" t="str">
+      <c r="U23">
+        <v>7</v>
+      </c>
+      <c r="V23">
+        <v>28</v>
+      </c>
+      <c r="W23" t="str">
         <v>Concrete</v>
       </c>
-      <c r="W23">
+      <c r="X23">
         <v>5</v>
       </c>
-      <c r="X23" t="str">
-        <v>152.00</v>
-      </c>
-      <c r="Y23" t="str">
-        <v>10.80</v>
+      <c r="Y23">
+        <v>152</v>
       </c>
       <c r="Z23">
+        <v>10.8</v>
+      </c>
+      <c r="AA23">
         <v>2</v>
       </c>
-      <c r="AA23" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB23">
+      <c r="AB23" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC23">
+        <v>3</v>
+      </c>
+      <c r="AD23">
         <v>5</v>
       </c>
-      <c r="AC23">
-        <v>5</v>
-      </c>
-      <c r="AD23" t="str">
+      <c r="AE23" t="str">
         <v>Restricted</v>
       </c>
-      <c r="AE23" t="str">
+      <c r="AF23" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF23" t="str">
+      <c r="AG23" t="str">
         <v>Zone 1</v>
-      </c>
-      <c r="AG23" t="str">
-        <v/>
       </c>
       <c r="AH23" t="str">
         <v/>
@@ -5740,43 +5865,43 @@
         <v>Ageing structure with precamber loss. Restricted to 30t GML pending detailed assessment scheduled for Q1 2026.</v>
       </c>
       <c r="AM23" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN23" t="str">
-        <v>Low</v>
-      </c>
-      <c r="AO23" t="str">
         <v>2025-07-04</v>
       </c>
-      <c r="AP23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ23" t="str">
+      <c r="AO23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="str">
         <v>2025-07-11</v>
       </c>
+      <c r="AQ23">
+        <v>29</v>
+      </c>
       <c r="AR23" t="str">
-        <v>29.00</v>
+        <v/>
       </c>
       <c r="AS23" t="str">
         <v/>
       </c>
-      <c r="AT23" t="str">
-        <v/>
+      <c r="AT23">
+        <v>5800</v>
       </c>
       <c r="AU23">
-        <v>5800</v>
+        <v>11</v>
       </c>
       <c r="AV23" t="str">
-        <v>11.00</v>
+        <v/>
       </c>
       <c r="AW23" t="str">
         <v/>
       </c>
-      <c r="AX23" t="str">
-        <v/>
+      <c r="AX23" t="b">
+        <v>1</v>
       </c>
       <c r="AY23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="b">
         <v>0</v>
@@ -5784,11 +5909,11 @@
       <c r="BA23" t="b">
         <v>0</v>
       </c>
-      <c r="BB23" t="b">
-        <v>0</v>
+      <c r="BB23" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC23" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD23" t="str">
         <v/>
@@ -5800,111 +5925,117 @@
         <v/>
       </c>
       <c r="BG23" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[149.796,-36.712],[149.802,-36.712]]}</v>
       </c>
       <c r="BH23" t="str">
-        <v>{"type":"LineString","coordinates":[[149.834,-36.676],[149.840,-36.676]]}</v>
+        <v/>
+      </c>
+      <c r="BI23" t="str">
+        <v/>
+      </c>
+      <c r="BJ23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>1023</v>
+      <c r="A24" t="str">
+        <v/>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
         <v>BRG-NSW-WST-001</v>
       </c>
-      <c r="D24" t="str">
-        <v>Darling River Bridge (Bourke)</v>
-      </c>
       <c r="E24" t="str">
+        <v>Dryfield River Bridge</v>
+      </c>
+      <c r="F24" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F24" t="str">
-        <v>Mitchell Highway</v>
-      </c>
       <c r="G24" t="str">
+        <v>Outback Highway</v>
+      </c>
+      <c r="H24" t="str">
         <v>A71</v>
       </c>
-      <c r="H24" t="str">
+      <c r="I24" t="str">
         <v>NSW</v>
       </c>
-      <c r="I24" t="str">
+      <c r="J24" t="str">
         <v>Far West NSW</v>
       </c>
-      <c r="J24" t="str">
-        <v>Bourke</v>
-      </c>
       <c r="K24" t="str">
-        <v>-30.091500</v>
-      </c>
-      <c r="L24" t="str">
-        <v>145.939800</v>
-      </c>
-      <c r="M24" t="str">
-        <v>Darling River</v>
+        <v>Dryfield</v>
+      </c>
+      <c r="L24">
+        <v>-30.1482</v>
+      </c>
+      <c r="M24">
+        <v>145.8864</v>
       </c>
       <c r="N24" t="str">
-        <v>Transport for NSW</v>
+        <v>Dryfield River</v>
       </c>
       <c r="O24" t="str">
-        <v>Transport for NSW</v>
+        <v>Dryfield Shire Council</v>
       </c>
       <c r="P24" t="str">
+        <v>Dryfield Shire Council</v>
+      </c>
+      <c r="Q24" t="str">
         <v>Truss Bridge</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>1902</v>
       </c>
-      <c r="R24" t="str">
+      <c r="S24" t="str">
         <v>T44</v>
       </c>
-      <c r="S24" t="str">
+      <c r="T24" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T24" t="str">
-        <v>6.20</v>
-      </c>
-      <c r="U24" t="str">
-        <v>71.00</v>
-      </c>
-      <c r="V24" t="str">
+      <c r="U24">
+        <v>6.2</v>
+      </c>
+      <c r="V24">
+        <v>71</v>
+      </c>
+      <c r="W24" t="str">
         <v>Steel</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <v>3</v>
       </c>
-      <c r="X24" t="str">
-        <v>230.00</v>
-      </c>
-      <c r="Y24" t="str">
-        <v>8.00</v>
+      <c r="Y24">
+        <v>230</v>
       </c>
       <c r="Z24">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="str">
-        <v>Poor</v>
-      </c>
-      <c r="AB24">
+        <v>8</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="str">
+        <v>5</v>
+      </c>
+      <c r="AC24">
+        <v>5</v>
+      </c>
+      <c r="AD24">
         <v>2</v>
       </c>
-      <c r="AC24">
-        <v>2</v>
-      </c>
-      <c r="AD24" t="str">
+      <c r="AE24" t="str">
         <v>Restricted</v>
       </c>
-      <c r="AE24" t="str">
+      <c r="AF24" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF24" t="str">
+      <c r="AG24" t="str">
         <v>Zone 0</v>
-      </c>
-      <c r="AG24" t="str">
-        <v/>
       </c>
       <c r="AH24" t="str">
         <v/>
@@ -5922,40 +6053,40 @@
         <v>122-year-old riveted wrought iron truss — rare surviving example. Heritage listed. Single lane — load restricted to 10t. Urgent structural intervention required.</v>
       </c>
       <c r="AM24" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN24" t="str">
-        <v>High</v>
-      </c>
-      <c r="AO24" t="str">
         <v>2025-06-05</v>
       </c>
-      <c r="AP24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="str">
-        <v/>
+      <c r="AO24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="str">
+        <v/>
+      </c>
+      <c r="AQ24">
+        <v>10</v>
       </c>
       <c r="AR24" t="str">
-        <v>10.00</v>
+        <v/>
       </c>
       <c r="AS24" t="str">
         <v/>
       </c>
-      <c r="AT24" t="str">
-        <v/>
+      <c r="AT24">
+        <v>850</v>
       </c>
       <c r="AU24">
-        <v>850</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="str">
-        <v>8.00</v>
+        <v/>
       </c>
       <c r="AW24" t="str">
         <v/>
       </c>
-      <c r="AX24" t="str">
-        <v/>
+      <c r="AX24" t="b">
+        <v>0</v>
       </c>
       <c r="AY24" t="b">
         <v>0</v>
@@ -5966,11 +6097,11 @@
       <c r="BA24" t="b">
         <v>0</v>
       </c>
-      <c r="BB24" t="b">
-        <v>0</v>
+      <c r="BB24" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC24" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD24" t="str">
         <v/>
@@ -5982,111 +6113,117 @@
         <v/>
       </c>
       <c r="BG24" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[145.883,-30.148],[145.890,-30.148]]}</v>
       </c>
       <c r="BH24" t="str">
-        <v>{"type":"LineString","coordinates":[[145.936,-30.092],[145.943,-30.092]]}</v>
+        <v/>
+      </c>
+      <c r="BI24" t="str">
+        <v/>
+      </c>
+      <c r="BJ24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>1024</v>
+      <c r="A25" t="str">
+        <v/>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
         <v>BRG-NSW-WST-002</v>
       </c>
-      <c r="D25" t="str">
-        <v>Lachlan River Bridge (Forbes)</v>
-      </c>
       <c r="E25" t="str">
+        <v>Wheatfield River Bridge</v>
+      </c>
+      <c r="F25" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F25" t="str">
-        <v>Newell Highway</v>
-      </c>
       <c r="G25" t="str">
+        <v>Inland Highway</v>
+      </c>
+      <c r="H25" t="str">
         <v>A39</v>
       </c>
-      <c r="H25" t="str">
+      <c r="I25" t="str">
         <v>NSW</v>
       </c>
-      <c r="I25" t="str">
+      <c r="J25" t="str">
         <v>Western NSW</v>
       </c>
-      <c r="J25" t="str">
-        <v>Forbes</v>
-      </c>
       <c r="K25" t="str">
-        <v>-33.378400</v>
-      </c>
-      <c r="L25" t="str">
-        <v>148.012200</v>
-      </c>
-      <c r="M25" t="str">
-        <v>Lachlan River</v>
+        <v>Wheatfield</v>
+      </c>
+      <c r="L25">
+        <v>-33.4246</v>
+      </c>
+      <c r="M25">
+        <v>148.0642</v>
       </c>
       <c r="N25" t="str">
-        <v>Transport for NSW</v>
+        <v>Wheatfield River</v>
       </c>
       <c r="O25" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="P25" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q25" t="str">
         <v>Prestressed Concrete Girder</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>1990</v>
       </c>
-      <c r="R25" t="str">
+      <c r="S25" t="str">
         <v>T44</v>
       </c>
-      <c r="S25" t="str">
+      <c r="T25" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T25" t="str">
-        <v>9.50</v>
-      </c>
-      <c r="U25" t="str">
-        <v>32.00</v>
-      </c>
-      <c r="V25" t="str">
+      <c r="U25">
+        <v>9.5</v>
+      </c>
+      <c r="V25">
+        <v>32</v>
+      </c>
+      <c r="W25" t="str">
         <v>Concrete</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <v>7</v>
       </c>
-      <c r="X25" t="str">
-        <v>238.00</v>
-      </c>
-      <c r="Y25" t="str">
-        <v>12.00</v>
+      <c r="Y25">
+        <v>238</v>
       </c>
       <c r="Z25">
+        <v>12</v>
+      </c>
+      <c r="AA25">
         <v>2</v>
       </c>
-      <c r="AA25" t="str">
-        <v>Good</v>
-      </c>
-      <c r="AB25">
+      <c r="AB25" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC25">
+        <v>2</v>
+      </c>
+      <c r="AD25">
         <v>7</v>
       </c>
-      <c r="AC25">
-        <v>7</v>
-      </c>
-      <c r="AD25" t="str">
+      <c r="AE25" t="str">
         <v>Unrestricted</v>
       </c>
-      <c r="AE25" t="str">
+      <c r="AF25" t="str">
         <v>AS 5100</v>
       </c>
-      <c r="AF25" t="str">
+      <c r="AG25" t="str">
         <v>Zone 0</v>
-      </c>
-      <c r="AG25" t="str">
-        <v/>
       </c>
       <c r="AH25" t="str">
         <v/>
@@ -6104,40 +6241,40 @@
         <v>Major grain belt crossing. Very high HV% reflects agricultural export freight. Bridge in good condition.</v>
       </c>
       <c r="AM25" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN25" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO25" t="str">
         <v>2025-10-22</v>
       </c>
-      <c r="AP25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ25" t="str">
+      <c r="AO25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="str">
         <v>2025-10-29</v>
       </c>
+      <c r="AQ25">
+        <v>38</v>
+      </c>
       <c r="AR25" t="str">
-        <v>38.00</v>
+        <v/>
       </c>
       <c r="AS25" t="str">
         <v/>
       </c>
-      <c r="AT25" t="str">
-        <v/>
+      <c r="AT25">
+        <v>4200</v>
       </c>
       <c r="AU25">
-        <v>4200</v>
+        <v>35</v>
       </c>
       <c r="AV25" t="str">
-        <v>35.00</v>
+        <v/>
       </c>
       <c r="AW25" t="str">
         <v/>
       </c>
-      <c r="AX25" t="str">
-        <v/>
+      <c r="AX25" t="b">
+        <v>1</v>
       </c>
       <c r="AY25" t="b">
         <v>1</v>
@@ -6148,1037 +6285,1073 @@
       <c r="BA25" t="b">
         <v>1</v>
       </c>
-      <c r="BB25" t="b">
-        <v>1</v>
+      <c r="BB25" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC25" t="str">
+        <v/>
+      </c>
+      <c r="BD25" t="str">
+        <v/>
+      </c>
+      <c r="BE25" t="str">
+        <v/>
+      </c>
+      <c r="BF25" t="str">
+        <v/>
+      </c>
+      <c r="BG25" t="str">
+        <v>{"type":"LineString","coordinates":[[148.061,-33.424],[148.067,-33.424]]}</v>
+      </c>
+      <c r="BH25" t="str">
+        <v/>
+      </c>
+      <c r="BI25" t="str">
+        <v/>
+      </c>
+      <c r="BJ25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v>BRG-NSW-WST-003</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Bindaree River Bridge</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Road Bridge</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Southern Cross Highway</v>
+      </c>
+      <c r="H26" t="str">
+        <v>B94</v>
+      </c>
+      <c r="I26" t="str">
+        <v>NSW</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Riverina</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Bindaree</v>
+      </c>
+      <c r="L26">
+        <v>-35.1486</v>
+      </c>
+      <c r="M26">
+        <v>147.3124</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Bindaree River</v>
+      </c>
+      <c r="O26" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P26" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>Prestressed Concrete Girder</v>
+      </c>
+      <c r="R26">
+        <v>1994</v>
+      </c>
+      <c r="S26" t="str">
+        <v>SM1600</v>
+      </c>
+      <c r="T26" t="str">
+        <v>AS5100</v>
+      </c>
+      <c r="U26">
+        <v>8.8</v>
+      </c>
+      <c r="V26">
+        <v>38</v>
+      </c>
+      <c r="W26" t="str">
+        <v>Concrete</v>
+      </c>
+      <c r="X26">
+        <v>9</v>
+      </c>
+      <c r="Y26">
+        <v>358</v>
+      </c>
+      <c r="Z26">
+        <v>12.8</v>
+      </c>
+      <c r="AA26">
+        <v>2</v>
+      </c>
+      <c r="AB26" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC26">
+        <v>2</v>
+      </c>
+      <c r="AD26">
+        <v>8</v>
+      </c>
+      <c r="AE26" t="str">
+        <v>Unrestricted</v>
+      </c>
+      <c r="AF26" t="str">
+        <v>AS 5100</v>
+      </c>
+      <c r="AG26" t="str">
+        <v>Zone 0</v>
+      </c>
+      <c r="AH26" t="str">
+        <v/>
+      </c>
+      <c r="AI26" t="str">
+        <v/>
+      </c>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="str">
+        <v>Regional highway crossing serving grain and livestock freight corridors to southern ports.</v>
+      </c>
+      <c r="AM26" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN26" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="AO26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="str">
+        <v>2025-11-09</v>
+      </c>
+      <c r="AQ26">
+        <v>40</v>
+      </c>
+      <c r="AR26" t="str">
+        <v/>
+      </c>
+      <c r="AS26" t="str">
+        <v/>
+      </c>
+      <c r="AT26">
+        <v>8900</v>
+      </c>
+      <c r="AU26">
+        <v>30</v>
+      </c>
+      <c r="AV26" t="str">
+        <v/>
+      </c>
+      <c r="AW26" t="str">
+        <v/>
+      </c>
+      <c r="AX26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ26" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA26" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB26" t="str">
         <v>DEMO</v>
       </c>
-      <c r="BD25" t="str">
-        <v/>
-      </c>
-      <c r="BE25" t="str">
-        <v/>
-      </c>
-      <c r="BF25" t="str">
-        <v/>
-      </c>
-      <c r="BG25" t="str">
-        <v/>
-      </c>
-      <c r="BH25" t="str">
-        <v>{"type":"LineString","coordinates":[[148.009,-33.378],[148.015,-33.378]]}</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>1025</v>
-      </c>
-      <c r="B26" t="str">
-        <v/>
-      </c>
-      <c r="C26" t="str">
-        <v>BRG-NSW-WST-003</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Murrumbidgee River Bridge (Wagga Wagga)</v>
-      </c>
-      <c r="E26" t="str">
+      <c r="BC26" t="str">
+        <v/>
+      </c>
+      <c r="BD26" t="str">
+        <v/>
+      </c>
+      <c r="BE26" t="str">
+        <v/>
+      </c>
+      <c r="BF26" t="str">
+        <v/>
+      </c>
+      <c r="BG26" t="str">
+        <v>{"type":"LineString","coordinates":[[147.309,-35.149],[147.316,-35.149]]}</v>
+      </c>
+      <c r="BH26" t="str">
+        <v/>
+      </c>
+      <c r="BI26" t="str">
+        <v/>
+      </c>
+      <c r="BJ26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v/>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>BRG-NSW-WST-004</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Borderton Bridge</v>
+      </c>
+      <c r="F27" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F26" t="str">
-        <v>Olympic Highway</v>
-      </c>
-      <c r="G26" t="str">
-        <v>B94</v>
-      </c>
-      <c r="H26" t="str">
+      <c r="G27" t="str">
+        <v>Southern Highway</v>
+      </c>
+      <c r="H27" t="str">
+        <v>A79</v>
+      </c>
+      <c r="I27" t="str">
         <v>NSW</v>
       </c>
-      <c r="I26" t="str">
+      <c r="J27" t="str">
         <v>Riverina</v>
       </c>
-      <c r="J26" t="str">
-        <v>Wagga Wagga</v>
-      </c>
-      <c r="K26" t="str">
-        <v>-35.109500</v>
-      </c>
-      <c r="L26" t="str">
-        <v>147.362800</v>
-      </c>
-      <c r="M26" t="str">
-        <v>Murrumbidgee River</v>
-      </c>
-      <c r="N26" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O26" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P26" t="str">
+      <c r="K27" t="str">
+        <v>Borderton</v>
+      </c>
+      <c r="L27">
+        <v>-36.0482</v>
+      </c>
+      <c r="M27">
+        <v>146.9486</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Border River (NSW/VIC border)</v>
+      </c>
+      <c r="O27" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P27" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q27" t="str">
         <v>Prestressed Concrete Girder</v>
       </c>
-      <c r="Q26">
-        <v>1994</v>
-      </c>
-      <c r="R26" t="str">
+      <c r="R27">
+        <v>1977</v>
+      </c>
+      <c r="S27" t="str">
+        <v>T44</v>
+      </c>
+      <c r="T27" t="str">
+        <v>AS5100</v>
+      </c>
+      <c r="U27">
+        <v>8.4</v>
+      </c>
+      <c r="V27">
+        <v>36</v>
+      </c>
+      <c r="W27" t="str">
+        <v>Concrete</v>
+      </c>
+      <c r="X27">
+        <v>10</v>
+      </c>
+      <c r="Y27">
+        <v>378</v>
+      </c>
+      <c r="Z27">
+        <v>13.6</v>
+      </c>
+      <c r="AA27">
+        <v>2</v>
+      </c>
+      <c r="AB27" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC27">
+        <v>3</v>
+      </c>
+      <c r="AD27">
+        <v>6</v>
+      </c>
+      <c r="AE27" t="str">
+        <v>Unrestricted</v>
+      </c>
+      <c r="AF27" t="str">
+        <v>AS 5100.7</v>
+      </c>
+      <c r="AG27" t="str">
+        <v>Zone 0</v>
+      </c>
+      <c r="AH27" t="str">
+        <v/>
+      </c>
+      <c r="AI27" t="str">
+        <v/>
+      </c>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="str">
+        <v>Inter-state border crossing on a major north-south freight corridor. Joint maintenance agreement between NSW and VIC.</v>
+      </c>
+      <c r="AM27" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN27" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="AO27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="str">
+        <v>2025-10-07</v>
+      </c>
+      <c r="AQ27">
+        <v>34.5</v>
+      </c>
+      <c r="AR27" t="str">
+        <v/>
+      </c>
+      <c r="AS27" t="str">
+        <v/>
+      </c>
+      <c r="AT27">
+        <v>22000</v>
+      </c>
+      <c r="AU27">
+        <v>27</v>
+      </c>
+      <c r="AV27" t="str">
+        <v/>
+      </c>
+      <c r="AW27" t="str">
+        <v/>
+      </c>
+      <c r="AX27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ27" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA27" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB27" t="str">
+        <v>DEMO</v>
+      </c>
+      <c r="BC27" t="str">
+        <v/>
+      </c>
+      <c r="BD27" t="str">
+        <v/>
+      </c>
+      <c r="BE27" t="str">
+        <v/>
+      </c>
+      <c r="BF27" t="str">
+        <v/>
+      </c>
+      <c r="BG27" t="str">
+        <v>{"type":"LineString","coordinates":[[146.946,-36.048],[146.952,-36.048]]}</v>
+      </c>
+      <c r="BH27" t="str">
+        <v/>
+      </c>
+      <c r="BI27" t="str">
+        <v/>
+      </c>
+      <c r="BJ27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>BRG-NSW-CTR-001</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Millbrook Bridge</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Road Bridge</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Western Highway</v>
+      </c>
+      <c r="H28" t="str">
+        <v>A32</v>
+      </c>
+      <c r="I28" t="str">
+        <v>NSW</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Central West</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Millbrook Regional</v>
+      </c>
+      <c r="L28">
+        <v>-33.4486</v>
+      </c>
+      <c r="M28">
+        <v>149.5124</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Millbrook River</v>
+      </c>
+      <c r="O28" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P28" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>Girder Bridge</v>
+      </c>
+      <c r="R28">
+        <v>2001</v>
+      </c>
+      <c r="S28" t="str">
         <v>SM1600</v>
       </c>
-      <c r="S26" t="str">
+      <c r="T28" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T26" t="str">
-        <v>8.80</v>
-      </c>
-      <c r="U26" t="str">
-        <v>38.00</v>
-      </c>
-      <c r="V26" t="str">
+      <c r="U28">
+        <v>6.8</v>
+      </c>
+      <c r="V28">
+        <v>28</v>
+      </c>
+      <c r="W28" t="str">
         <v>Concrete</v>
       </c>
-      <c r="W26">
+      <c r="X28">
+        <v>4</v>
+      </c>
+      <c r="Y28">
+        <v>118</v>
+      </c>
+      <c r="Z28">
+        <v>14.2</v>
+      </c>
+      <c r="AA28">
+        <v>4</v>
+      </c>
+      <c r="AB28" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC28">
+        <v>2</v>
+      </c>
+      <c r="AD28">
+        <v>8</v>
+      </c>
+      <c r="AE28" t="str">
+        <v>Unrestricted</v>
+      </c>
+      <c r="AF28" t="str">
+        <v>AS 5100</v>
+      </c>
+      <c r="AG28" t="str">
+        <v>Zone 0</v>
+      </c>
+      <c r="AH28" t="str">
+        <v/>
+      </c>
+      <c r="AI28" t="str">
+        <v/>
+      </c>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="str">
+        <v>4-lane divided highway structure in good condition. Major regional freight and tourism route.</v>
+      </c>
+      <c r="AM28" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN28" t="str">
+        <v>2025-11-06</v>
+      </c>
+      <c r="AO28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="str">
+        <v>2025-11-12</v>
+      </c>
+      <c r="AQ28">
+        <v>42</v>
+      </c>
+      <c r="AR28" t="str">
+        <v/>
+      </c>
+      <c r="AS28" t="str">
+        <v/>
+      </c>
+      <c r="AT28">
+        <v>35000</v>
+      </c>
+      <c r="AU28">
+        <v>19</v>
+      </c>
+      <c r="AV28" t="str">
+        <v/>
+      </c>
+      <c r="AW28" t="str">
+        <v/>
+      </c>
+      <c r="AX28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ28" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA28" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB28" t="str">
+        <v>DEMO</v>
+      </c>
+      <c r="BC28" t="str">
+        <v/>
+      </c>
+      <c r="BD28" t="str">
+        <v/>
+      </c>
+      <c r="BE28" t="str">
+        <v/>
+      </c>
+      <c r="BF28" t="str">
+        <v/>
+      </c>
+      <c r="BG28" t="str">
+        <v>{"type":"LineString","coordinates":[[149.509,-33.448],[149.516,-33.448]]}</v>
+      </c>
+      <c r="BH28" t="str">
+        <v/>
+      </c>
+      <c r="BI28" t="str">
+        <v/>
+      </c>
+      <c r="BJ28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>BRG-NSW-CTR-002</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Hartley Gorge Bridge</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Road Bridge</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Western Highway</v>
+      </c>
+      <c r="H29" t="str">
+        <v>A32</v>
+      </c>
+      <c r="I29" t="str">
+        <v>NSW</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Central West</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Hartley</v>
+      </c>
+      <c r="L29">
+        <v>-33.5246</v>
+      </c>
+      <c r="M29">
+        <v>150.0648</v>
+      </c>
+      <c r="N29" t="str">
+        <v>Hartley Gorge</v>
+      </c>
+      <c r="O29" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P29" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>Box Girder Bridge</v>
+      </c>
+      <c r="R29">
+        <v>2006</v>
+      </c>
+      <c r="S29" t="str">
+        <v>SM1600</v>
+      </c>
+      <c r="T29" t="str">
+        <v>AS5100</v>
+      </c>
+      <c r="U29">
+        <v>14.6</v>
+      </c>
+      <c r="V29">
+        <v>60</v>
+      </c>
+      <c r="W29" t="str">
+        <v>Concrete</v>
+      </c>
+      <c r="X29">
+        <v>3</v>
+      </c>
+      <c r="Y29">
+        <v>194</v>
+      </c>
+      <c r="Z29">
+        <v>13.8</v>
+      </c>
+      <c r="AA29">
+        <v>4</v>
+      </c>
+      <c r="AB29" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC29">
+        <v>1</v>
+      </c>
+      <c r="AD29">
         <v>9</v>
       </c>
-      <c r="X26" t="str">
-        <v>358.00</v>
-      </c>
-      <c r="Y26" t="str">
-        <v>12.80</v>
-      </c>
-      <c r="Z26">
+      <c r="AE29" t="str">
+        <v>Unrestricted</v>
+      </c>
+      <c r="AF29" t="str">
+        <v>AS 5100</v>
+      </c>
+      <c r="AG29" t="str">
+        <v>Zone 0</v>
+      </c>
+      <c r="AH29" t="str">
+        <v/>
+      </c>
+      <c r="AI29" t="str">
+        <v/>
+      </c>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="str">
+        <v>Modern box girder in excellent condition. Part of a highway duplication project.</v>
+      </c>
+      <c r="AM29" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN29" t="str">
+        <v>2025-10-27</v>
+      </c>
+      <c r="AO29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="str">
+        <v>2025-11-02</v>
+      </c>
+      <c r="AQ29">
+        <v>45</v>
+      </c>
+      <c r="AR29" t="str">
+        <v/>
+      </c>
+      <c r="AS29" t="str">
+        <v/>
+      </c>
+      <c r="AT29">
+        <v>28000</v>
+      </c>
+      <c r="AU29">
+        <v>17</v>
+      </c>
+      <c r="AV29" t="str">
+        <v/>
+      </c>
+      <c r="AW29" t="str">
+        <v/>
+      </c>
+      <c r="AX29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ29" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA29" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB29" t="str">
+        <v>DEMO</v>
+      </c>
+      <c r="BC29" t="str">
+        <v/>
+      </c>
+      <c r="BD29" t="str">
+        <v/>
+      </c>
+      <c r="BE29" t="str">
+        <v/>
+      </c>
+      <c r="BF29" t="str">
+        <v/>
+      </c>
+      <c r="BG29" t="str">
+        <v>{"type":"LineString","coordinates":[[150.062,-33.525],[150.068,-33.525]]}</v>
+      </c>
+      <c r="BH29" t="str">
+        <v/>
+      </c>
+      <c r="BI29" t="str">
+        <v/>
+      </c>
+      <c r="BJ29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v>BRG-NSW-SWS-001</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Riverford Bridge</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Road Bridge</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Southern Highway</v>
+      </c>
+      <c r="H30" t="str">
+        <v>A79</v>
+      </c>
+      <c r="I30" t="str">
+        <v>NSW</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Riverina</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Riverford</v>
+      </c>
+      <c r="L30">
+        <v>-35.0986</v>
+      </c>
+      <c r="M30">
+        <v>148.1524</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Bindaree River</v>
+      </c>
+      <c r="O30" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="P30" t="str">
+        <v>State Roads Authority</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>Prestressed Concrete Girder</v>
+      </c>
+      <c r="R30">
+        <v>1978</v>
+      </c>
+      <c r="S30" t="str">
+        <v>T44</v>
+      </c>
+      <c r="T30" t="str">
+        <v>AS5100</v>
+      </c>
+      <c r="U30">
+        <v>11.2</v>
+      </c>
+      <c r="V30">
+        <v>36</v>
+      </c>
+      <c r="W30" t="str">
+        <v>Concrete</v>
+      </c>
+      <c r="X30">
+        <v>11</v>
+      </c>
+      <c r="Y30">
+        <v>414</v>
+      </c>
+      <c r="Z30">
+        <v>12.2</v>
+      </c>
+      <c r="AA30">
         <v>2</v>
       </c>
-      <c r="AA26" t="str">
-        <v>Good</v>
-      </c>
-      <c r="AB26">
-        <v>8</v>
-      </c>
-      <c r="AC26">
-        <v>8</v>
-      </c>
-      <c r="AD26" t="str">
+      <c r="AB30" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC30">
+        <v>3</v>
+      </c>
+      <c r="AD30">
+        <v>6</v>
+      </c>
+      <c r="AE30" t="str">
         <v>Unrestricted</v>
       </c>
-      <c r="AE26" t="str">
-        <v>AS 5100</v>
-      </c>
-      <c r="AF26" t="str">
+      <c r="AF30" t="str">
+        <v>AS 5100.7</v>
+      </c>
+      <c r="AG30" t="str">
         <v>Zone 0</v>
       </c>
-      <c r="AG26" t="str">
-        <v/>
-      </c>
-      <c r="AH26" t="str">
-        <v/>
-      </c>
-      <c r="AI26" t="str">
-        <v/>
-      </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="str">
-        <v>Olympic Highway crossing. Serves Riverina grain and livestock freight corridor to Port of Melbourne.</v>
-      </c>
-      <c r="AM26" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN26" t="str">
-        <v>Low</v>
-      </c>
-      <c r="AO26" t="str">
-        <v>2025-11-03</v>
-      </c>
-      <c r="AP26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ26" t="str">
-        <v>2025-11-09</v>
-      </c>
-      <c r="AR26" t="str">
-        <v>40.00</v>
-      </c>
-      <c r="AS26" t="str">
-        <v/>
-      </c>
-      <c r="AT26" t="str">
-        <v/>
-      </c>
-      <c r="AU26">
-        <v>8900</v>
-      </c>
-      <c r="AV26" t="str">
-        <v>30.00</v>
-      </c>
-      <c r="AW26" t="str">
-        <v/>
-      </c>
-      <c r="AX26" t="str">
-        <v/>
-      </c>
-      <c r="AY26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ26" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA26" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB26" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC26" t="str">
+      <c r="AH30" t="str">
+        <v/>
+      </c>
+      <c r="AI30" t="str">
+        <v/>
+      </c>
+      <c r="AJ30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="str">
+        <v>Main interstate truck corridor crossing. Major flooding history. Scour monitoring active on Piers 4 and 5.</v>
+      </c>
+      <c r="AM30" t="str">
+        <v>Active</v>
+      </c>
+      <c r="AN30" t="str">
+        <v>2025-09-15</v>
+      </c>
+      <c r="AO30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP30" t="str">
+        <v>2025-09-22</v>
+      </c>
+      <c r="AQ30">
+        <v>34</v>
+      </c>
+      <c r="AR30" t="str">
+        <v/>
+      </c>
+      <c r="AS30" t="str">
+        <v/>
+      </c>
+      <c r="AT30">
+        <v>19500</v>
+      </c>
+      <c r="AU30">
+        <v>25</v>
+      </c>
+      <c r="AV30" t="str">
+        <v/>
+      </c>
+      <c r="AW30" t="str">
+        <v/>
+      </c>
+      <c r="AX30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA30" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB30" t="str">
         <v>DEMO</v>
       </c>
-      <c r="BD26" t="str">
-        <v/>
-      </c>
-      <c r="BE26" t="str">
-        <v/>
-      </c>
-      <c r="BF26" t="str">
-        <v/>
-      </c>
-      <c r="BG26" t="str">
-        <v/>
-      </c>
-      <c r="BH26" t="str">
-        <v>{"type":"LineString","coordinates":[[147.359,-35.110],[147.366,-35.110]]}</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>1026</v>
-      </c>
-      <c r="B27" t="str">
-        <v/>
-      </c>
-      <c r="C27" t="str">
-        <v>BRG-NSW-WST-004</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Murray River Bridge (Albury)</v>
-      </c>
-      <c r="E27" t="str">
+      <c r="BC30" t="str">
+        <v/>
+      </c>
+      <c r="BD30" t="str">
+        <v/>
+      </c>
+      <c r="BE30" t="str">
+        <v/>
+      </c>
+      <c r="BF30" t="str">
+        <v/>
+      </c>
+      <c r="BG30" t="str">
+        <v>{"type":"LineString","coordinates":[[148.149,-35.099],[148.156,-35.099]]}</v>
+      </c>
+      <c r="BH30" t="str">
+        <v/>
+      </c>
+      <c r="BI30" t="str">
+        <v/>
+      </c>
+      <c r="BJ30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v/>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v>BRG-NSW-SWS-002</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Alpine Creek Bridge</v>
+      </c>
+      <c r="F31" t="str">
         <v>Road Bridge</v>
       </c>
-      <c r="F27" t="str">
-        <v>Hume Highway</v>
-      </c>
-      <c r="G27" t="str">
-        <v>A79</v>
-      </c>
-      <c r="H27" t="str">
+      <c r="G31" t="str">
+        <v>Alpine Highway</v>
+      </c>
+      <c r="H31" t="str">
+        <v>B72</v>
+      </c>
+      <c r="I31" t="str">
         <v>NSW</v>
       </c>
-      <c r="I27" t="str">
+      <c r="J31" t="str">
         <v>Riverina</v>
       </c>
-      <c r="J27" t="str">
-        <v>Albury</v>
-      </c>
-      <c r="K27" t="str">
-        <v>-36.079400</v>
-      </c>
-      <c r="L27" t="str">
-        <v>146.915200</v>
-      </c>
-      <c r="M27" t="str">
-        <v>Murray River (NSW/VIC Border)</v>
-      </c>
-      <c r="N27" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O27" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P27" t="str">
-        <v>Prestressed Concrete Girder</v>
-      </c>
-      <c r="Q27">
-        <v>1977</v>
-      </c>
-      <c r="R27" t="str">
+      <c r="K31" t="str">
+        <v>Alpine Valleys</v>
+      </c>
+      <c r="L31">
+        <v>-35.3482</v>
+      </c>
+      <c r="M31">
+        <v>148.2646</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Alpine Creek</v>
+      </c>
+      <c r="O31" t="str">
+        <v>Alpine Valleys Council</v>
+      </c>
+      <c r="P31" t="str">
+        <v>Alpine Valleys Council</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>Truss Bridge</v>
+      </c>
+      <c r="R31">
+        <v>1948</v>
+      </c>
+      <c r="S31" t="str">
         <v>T44</v>
       </c>
-      <c r="S27" t="str">
+      <c r="T31" t="str">
         <v>AS5100</v>
       </c>
-      <c r="T27" t="str">
-        <v>8.40</v>
-      </c>
-      <c r="U27" t="str">
-        <v>36.00</v>
-      </c>
-      <c r="V27" t="str">
-        <v>Concrete</v>
-      </c>
-      <c r="W27">
-        <v>10</v>
-      </c>
-      <c r="X27" t="str">
-        <v>378.00</v>
-      </c>
-      <c r="Y27" t="str">
-        <v>13.60</v>
-      </c>
-      <c r="Z27">
+      <c r="U31">
+        <v>8.4</v>
+      </c>
+      <c r="V31">
+        <v>55</v>
+      </c>
+      <c r="W31" t="str">
+        <v>Steel</v>
+      </c>
+      <c r="X31">
         <v>2</v>
       </c>
-      <c r="AA27" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB27">
-        <v>6</v>
-      </c>
-      <c r="AC27">
-        <v>6</v>
-      </c>
-      <c r="AD27" t="str">
-        <v>Unrestricted</v>
-      </c>
-      <c r="AE27" t="str">
+      <c r="Y31">
+        <v>128</v>
+      </c>
+      <c r="Z31">
+        <v>8.6</v>
+      </c>
+      <c r="AA31">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="str">
+        <v>4</v>
+      </c>
+      <c r="AC31">
+        <v>4</v>
+      </c>
+      <c r="AD31">
+        <v>3</v>
+      </c>
+      <c r="AE31" t="str">
+        <v>Restricted</v>
+      </c>
+      <c r="AF31" t="str">
         <v>AS 5100.7</v>
       </c>
-      <c r="AF27" t="str">
+      <c r="AG31" t="str">
         <v>Zone 0</v>
-      </c>
-      <c r="AG27" t="str">
-        <v/>
-      </c>
-      <c r="AH27" t="str">
-        <v/>
-      </c>
-      <c r="AI27" t="str">
-        <v/>
-      </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL27" t="str">
-        <v>Inter-state border crossing on main Sydney-Melbourne corridor. Joint maintenance agreement between NSW and VIC.</v>
-      </c>
-      <c r="AM27" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN27" t="str">
-        <v>Low</v>
-      </c>
-      <c r="AO27" t="str">
-        <v>2025-09-30</v>
-      </c>
-      <c r="AP27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ27" t="str">
-        <v>2025-10-07</v>
-      </c>
-      <c r="AR27" t="str">
-        <v>34.50</v>
-      </c>
-      <c r="AS27" t="str">
-        <v/>
-      </c>
-      <c r="AT27" t="str">
-        <v/>
-      </c>
-      <c r="AU27">
-        <v>22000</v>
-      </c>
-      <c r="AV27" t="str">
-        <v>27.00</v>
-      </c>
-      <c r="AW27" t="str">
-        <v/>
-      </c>
-      <c r="AX27" t="str">
-        <v/>
-      </c>
-      <c r="AY27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ27" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA27" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB27" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC27" t="str">
-        <v>DEMO</v>
-      </c>
-      <c r="BD27" t="str">
-        <v/>
-      </c>
-      <c r="BE27" t="str">
-        <v/>
-      </c>
-      <c r="BF27" t="str">
-        <v/>
-      </c>
-      <c r="BG27" t="str">
-        <v/>
-      </c>
-      <c r="BH27" t="str">
-        <v>{"type":"LineString","coordinates":[[146.912,-36.079],[146.918,-36.079]]}</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>1027</v>
-      </c>
-      <c r="B28" t="str">
-        <v/>
-      </c>
-      <c r="C28" t="str">
-        <v>BRG-NSW-CTR-001</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Fish River Bridge (Bathurst)</v>
-      </c>
-      <c r="E28" t="str">
-        <v>Road Bridge</v>
-      </c>
-      <c r="F28" t="str">
-        <v>Great Western Highway</v>
-      </c>
-      <c r="G28" t="str">
-        <v>A32</v>
-      </c>
-      <c r="H28" t="str">
-        <v>NSW</v>
-      </c>
-      <c r="I28" t="str">
-        <v>Central West</v>
-      </c>
-      <c r="J28" t="str">
-        <v>Bathurst Regional</v>
-      </c>
-      <c r="K28" t="str">
-        <v>-33.420200</v>
-      </c>
-      <c r="L28" t="str">
-        <v>149.572600</v>
-      </c>
-      <c r="M28" t="str">
-        <v>Fish River</v>
-      </c>
-      <c r="N28" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O28" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P28" t="str">
-        <v>Girder Bridge</v>
-      </c>
-      <c r="Q28">
-        <v>2001</v>
-      </c>
-      <c r="R28" t="str">
-        <v>SM1600</v>
-      </c>
-      <c r="S28" t="str">
-        <v>AS5100</v>
-      </c>
-      <c r="T28" t="str">
-        <v>6.80</v>
-      </c>
-      <c r="U28" t="str">
-        <v>28.00</v>
-      </c>
-      <c r="V28" t="str">
-        <v>Concrete</v>
-      </c>
-      <c r="W28">
-        <v>4</v>
-      </c>
-      <c r="X28" t="str">
-        <v>118.00</v>
-      </c>
-      <c r="Y28" t="str">
-        <v>14.20</v>
-      </c>
-      <c r="Z28">
-        <v>4</v>
-      </c>
-      <c r="AA28" t="str">
-        <v>Good</v>
-      </c>
-      <c r="AB28">
-        <v>8</v>
-      </c>
-      <c r="AC28">
-        <v>8</v>
-      </c>
-      <c r="AD28" t="str">
-        <v>Unrestricted</v>
-      </c>
-      <c r="AE28" t="str">
-        <v>AS 5100</v>
-      </c>
-      <c r="AF28" t="str">
-        <v>Zone 0</v>
-      </c>
-      <c r="AG28" t="str">
-        <v/>
-      </c>
-      <c r="AH28" t="str">
-        <v/>
-      </c>
-      <c r="AI28" t="str">
-        <v/>
-      </c>
-      <c r="AJ28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="str">
-        <v>4-lane divided highway structure in good condition. Major Sydney–Bathurst–Dubbo freight and tourism route.</v>
-      </c>
-      <c r="AM28" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN28" t="str">
-        <v>Low</v>
-      </c>
-      <c r="AO28" t="str">
-        <v>2025-11-06</v>
-      </c>
-      <c r="AP28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ28" t="str">
-        <v>2025-11-12</v>
-      </c>
-      <c r="AR28" t="str">
-        <v>42.00</v>
-      </c>
-      <c r="AS28" t="str">
-        <v/>
-      </c>
-      <c r="AT28" t="str">
-        <v/>
-      </c>
-      <c r="AU28">
-        <v>35000</v>
-      </c>
-      <c r="AV28" t="str">
-        <v>19.00</v>
-      </c>
-      <c r="AW28" t="str">
-        <v/>
-      </c>
-      <c r="AX28" t="str">
-        <v/>
-      </c>
-      <c r="AY28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ28" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA28" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB28" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC28" t="str">
-        <v>DEMO</v>
-      </c>
-      <c r="BD28" t="str">
-        <v/>
-      </c>
-      <c r="BE28" t="str">
-        <v/>
-      </c>
-      <c r="BF28" t="str">
-        <v/>
-      </c>
-      <c r="BG28" t="str">
-        <v/>
-      </c>
-      <c r="BH28" t="str">
-        <v>{"type":"LineString","coordinates":[[149.569,-33.420],[149.576,-33.420]]}</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>1028</v>
-      </c>
-      <c r="B29" t="str">
-        <v/>
-      </c>
-      <c r="C29" t="str">
-        <v>BRG-NSW-CTR-002</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Cox River Bridge (Lithgow)</v>
-      </c>
-      <c r="E29" t="str">
-        <v>Road Bridge</v>
-      </c>
-      <c r="F29" t="str">
-        <v>Great Western Highway</v>
-      </c>
-      <c r="G29" t="str">
-        <v>A32</v>
-      </c>
-      <c r="H29" t="str">
-        <v>NSW</v>
-      </c>
-      <c r="I29" t="str">
-        <v>Central West</v>
-      </c>
-      <c r="J29" t="str">
-        <v>Lithgow</v>
-      </c>
-      <c r="K29" t="str">
-        <v>-33.492800</v>
-      </c>
-      <c r="L29" t="str">
-        <v>150.112400</v>
-      </c>
-      <c r="M29" t="str">
-        <v>Cox River</v>
-      </c>
-      <c r="N29" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O29" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P29" t="str">
-        <v>Box Girder Bridge</v>
-      </c>
-      <c r="Q29">
-        <v>2006</v>
-      </c>
-      <c r="R29" t="str">
-        <v>SM1600</v>
-      </c>
-      <c r="S29" t="str">
-        <v>AS5100</v>
-      </c>
-      <c r="T29" t="str">
-        <v>14.60</v>
-      </c>
-      <c r="U29" t="str">
-        <v>60.00</v>
-      </c>
-      <c r="V29" t="str">
-        <v>Concrete</v>
-      </c>
-      <c r="W29">
-        <v>3</v>
-      </c>
-      <c r="X29" t="str">
-        <v>194.00</v>
-      </c>
-      <c r="Y29" t="str">
-        <v>13.80</v>
-      </c>
-      <c r="Z29">
-        <v>4</v>
-      </c>
-      <c r="AA29" t="str">
-        <v>Excellent</v>
-      </c>
-      <c r="AB29">
-        <v>9</v>
-      </c>
-      <c r="AC29">
-        <v>9</v>
-      </c>
-      <c r="AD29" t="str">
-        <v>Unrestricted</v>
-      </c>
-      <c r="AE29" t="str">
-        <v>AS 5100</v>
-      </c>
-      <c r="AF29" t="str">
-        <v>Zone 0</v>
-      </c>
-      <c r="AG29" t="str">
-        <v/>
-      </c>
-      <c r="AH29" t="str">
-        <v/>
-      </c>
-      <c r="AI29" t="str">
-        <v/>
-      </c>
-      <c r="AJ29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="str">
-        <v>Modern box girder in excellent condition. Part of the Great Western Highway duplication project.</v>
-      </c>
-      <c r="AM29" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN29" t="str">
-        <v>Low</v>
-      </c>
-      <c r="AO29" t="str">
-        <v>2025-10-27</v>
-      </c>
-      <c r="AP29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ29" t="str">
-        <v>2025-11-02</v>
-      </c>
-      <c r="AR29" t="str">
-        <v>45.00</v>
-      </c>
-      <c r="AS29" t="str">
-        <v/>
-      </c>
-      <c r="AT29" t="str">
-        <v/>
-      </c>
-      <c r="AU29">
-        <v>28000</v>
-      </c>
-      <c r="AV29" t="str">
-        <v>17.00</v>
-      </c>
-      <c r="AW29" t="str">
-        <v/>
-      </c>
-      <c r="AX29" t="str">
-        <v/>
-      </c>
-      <c r="AY29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ29" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA29" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB29" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC29" t="str">
-        <v>DEMO</v>
-      </c>
-      <c r="BD29" t="str">
-        <v/>
-      </c>
-      <c r="BE29" t="str">
-        <v/>
-      </c>
-      <c r="BF29" t="str">
-        <v/>
-      </c>
-      <c r="BG29" t="str">
-        <v/>
-      </c>
-      <c r="BH29" t="str">
-        <v>{"type":"LineString","coordinates":[[150.109,-33.493],[150.115,-33.493]]}</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>1029</v>
-      </c>
-      <c r="B30" t="str">
-        <v/>
-      </c>
-      <c r="C30" t="str">
-        <v>BRG-NSW-SWS-001</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Murrumbidgee River Bridge (Gundagai)</v>
-      </c>
-      <c r="E30" t="str">
-        <v>Road Bridge</v>
-      </c>
-      <c r="F30" t="str">
-        <v>Hume Highway</v>
-      </c>
-      <c r="G30" t="str">
-        <v>A79</v>
-      </c>
-      <c r="H30" t="str">
-        <v>NSW</v>
-      </c>
-      <c r="I30" t="str">
-        <v>Riverina</v>
-      </c>
-      <c r="J30" t="str">
-        <v>Cootamundra-Gundagai</v>
-      </c>
-      <c r="K30" t="str">
-        <v>-35.063000</v>
-      </c>
-      <c r="L30" t="str">
-        <v>148.106700</v>
-      </c>
-      <c r="M30" t="str">
-        <v>Murrumbidgee River</v>
-      </c>
-      <c r="N30" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O30" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P30" t="str">
-        <v>Prestressed Concrete Girder</v>
-      </c>
-      <c r="Q30">
-        <v>1978</v>
-      </c>
-      <c r="R30" t="str">
-        <v>T44</v>
-      </c>
-      <c r="S30" t="str">
-        <v>AS5100</v>
-      </c>
-      <c r="T30" t="str">
-        <v>11.20</v>
-      </c>
-      <c r="U30" t="str">
-        <v>36.00</v>
-      </c>
-      <c r="V30" t="str">
-        <v>Concrete</v>
-      </c>
-      <c r="W30">
-        <v>11</v>
-      </c>
-      <c r="X30" t="str">
-        <v>414.00</v>
-      </c>
-      <c r="Y30" t="str">
-        <v>12.20</v>
-      </c>
-      <c r="Z30">
-        <v>2</v>
-      </c>
-      <c r="AA30" t="str">
-        <v>Fair</v>
-      </c>
-      <c r="AB30">
-        <v>6</v>
-      </c>
-      <c r="AC30">
-        <v>6</v>
-      </c>
-      <c r="AD30" t="str">
-        <v>Unrestricted</v>
-      </c>
-      <c r="AE30" t="str">
-        <v>AS 5100.7</v>
-      </c>
-      <c r="AF30" t="str">
-        <v>Zone 0</v>
-      </c>
-      <c r="AG30" t="str">
-        <v/>
-      </c>
-      <c r="AH30" t="str">
-        <v/>
-      </c>
-      <c r="AI30" t="str">
-        <v/>
-      </c>
-      <c r="AJ30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL30" t="str">
-        <v>Main Sydney-Melbourne truck corridor. Major flooding history. Scour monitoring active on Piers 4 and 5.</v>
-      </c>
-      <c r="AM30" t="str">
-        <v>Open</v>
-      </c>
-      <c r="AN30" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO30" t="str">
-        <v>2025-09-15</v>
-      </c>
-      <c r="AP30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ30" t="str">
-        <v>2025-09-22</v>
-      </c>
-      <c r="AR30" t="str">
-        <v>34.00</v>
-      </c>
-      <c r="AS30" t="str">
-        <v/>
-      </c>
-      <c r="AT30" t="str">
-        <v/>
-      </c>
-      <c r="AU30">
-        <v>19500</v>
-      </c>
-      <c r="AV30" t="str">
-        <v>25.00</v>
-      </c>
-      <c r="AW30" t="str">
-        <v/>
-      </c>
-      <c r="AX30" t="str">
-        <v/>
-      </c>
-      <c r="AY30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ30" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB30" t="b">
-        <v>1</v>
-      </c>
-      <c r="BC30" t="str">
-        <v>DEMO</v>
-      </c>
-      <c r="BD30" t="str">
-        <v/>
-      </c>
-      <c r="BE30" t="str">
-        <v/>
-      </c>
-      <c r="BF30" t="str">
-        <v/>
-      </c>
-      <c r="BG30" t="str">
-        <v/>
-      </c>
-      <c r="BH30" t="str">
-        <v>{"type":"LineString","coordinates":[[148.103,-35.063],[148.110,-35.063]]}</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>1030</v>
-      </c>
-      <c r="B31" t="str">
-        <v/>
-      </c>
-      <c r="C31" t="str">
-        <v>BRG-NSW-SWS-002</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Tumut River Bridge</v>
-      </c>
-      <c r="E31" t="str">
-        <v>Road Bridge</v>
-      </c>
-      <c r="F31" t="str">
-        <v>Snowy Mountains Highway</v>
-      </c>
-      <c r="G31" t="str">
-        <v>B72</v>
-      </c>
-      <c r="H31" t="str">
-        <v>NSW</v>
-      </c>
-      <c r="I31" t="str">
-        <v>Riverina</v>
-      </c>
-      <c r="J31" t="str">
-        <v>Snowy Valleys</v>
-      </c>
-      <c r="K31" t="str">
-        <v>-35.296600</v>
-      </c>
-      <c r="L31" t="str">
-        <v>148.221500</v>
-      </c>
-      <c r="M31" t="str">
-        <v>Tumut River</v>
-      </c>
-      <c r="N31" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="O31" t="str">
-        <v>Transport for NSW</v>
-      </c>
-      <c r="P31" t="str">
-        <v>Truss Bridge</v>
-      </c>
-      <c r="Q31">
-        <v>1948</v>
-      </c>
-      <c r="R31" t="str">
-        <v>T44</v>
-      </c>
-      <c r="S31" t="str">
-        <v>AS5100</v>
-      </c>
-      <c r="T31" t="str">
-        <v>8.40</v>
-      </c>
-      <c r="U31" t="str">
-        <v>55.00</v>
-      </c>
-      <c r="V31" t="str">
-        <v>Steel</v>
-      </c>
-      <c r="W31">
-        <v>2</v>
-      </c>
-      <c r="X31" t="str">
-        <v>128.00</v>
-      </c>
-      <c r="Y31" t="str">
-        <v>8.60</v>
-      </c>
-      <c r="Z31">
-        <v>1</v>
-      </c>
-      <c r="AA31" t="str">
-        <v>Poor</v>
-      </c>
-      <c r="AB31">
-        <v>3</v>
-      </c>
-      <c r="AC31">
-        <v>3</v>
-      </c>
-      <c r="AD31" t="str">
-        <v>Restricted</v>
-      </c>
-      <c r="AE31" t="str">
-        <v>AS 5100.7</v>
-      </c>
-      <c r="AF31" t="str">
-        <v>Zone 0</v>
-      </c>
-      <c r="AG31" t="str">
-        <v/>
       </c>
       <c r="AH31" t="str">
         <v/>
@@ -7196,40 +7369,40 @@
         <v>77-year-old single-lane steel truss. Corroded lower chord. Load limit 17t. Timber approaches replaced 2019.</v>
       </c>
       <c r="AM31" t="str">
-        <v>Open</v>
+        <v>Active</v>
       </c>
       <c r="AN31" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="AO31" t="str">
         <v>2025-05-08</v>
       </c>
-      <c r="AP31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="str">
-        <v/>
+      <c r="AO31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="str">
+        <v/>
+      </c>
+      <c r="AQ31">
+        <v>17</v>
       </c>
       <c r="AR31" t="str">
-        <v>17.00</v>
+        <v/>
       </c>
       <c r="AS31" t="str">
         <v/>
       </c>
-      <c r="AT31" t="str">
-        <v/>
+      <c r="AT31">
+        <v>3200</v>
       </c>
       <c r="AU31">
-        <v>3200</v>
+        <v>16</v>
       </c>
       <c r="AV31" t="str">
-        <v>16.00</v>
+        <v/>
       </c>
       <c r="AW31" t="str">
         <v/>
       </c>
-      <c r="AX31" t="str">
-        <v/>
+      <c r="AX31" t="b">
+        <v>0</v>
       </c>
       <c r="AY31" t="b">
         <v>0</v>
@@ -7240,11 +7413,11 @@
       <c r="BA31" t="b">
         <v>0</v>
       </c>
-      <c r="BB31" t="b">
-        <v>0</v>
+      <c r="BB31" t="str">
+        <v>DEMO</v>
       </c>
       <c r="BC31" t="str">
-        <v>DEMO</v>
+        <v/>
       </c>
       <c r="BD31" t="str">
         <v/>
@@ -7256,10 +7429,16 @@
         <v/>
       </c>
       <c r="BG31" t="str">
-        <v/>
+        <v>{"type":"LineString","coordinates":[[148.262,-35.348],[148.268,-35.348]]}</v>
       </c>
       <c r="BH31" t="str">
-        <v>{"type":"LineString","coordinates":[[148.218,-35.297],[148.225,-35.297]]}</v>
+        <v/>
+      </c>
+      <c r="BI31" t="str">
+        <v/>
+      </c>
+      <c r="BJ31" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -7574,13 +7753,13 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>TfNSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AA2" t="str">
         <v>Both Directions</v>
       </c>
       <c r="AB2" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AC2" t="str">
         <v/>
@@ -7595,7 +7774,7 @@
         <v/>
       </c>
       <c r="AG2" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AH2" t="str">
         <v/>
@@ -7741,13 +7920,13 @@
         <v/>
       </c>
       <c r="Z3" t="str">
-        <v>TfNSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AA3" t="str">
         <v>Both Directions</v>
       </c>
       <c r="AB3" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AC3" t="str">
         <v/>
@@ -7762,7 +7941,7 @@
         <v/>
       </c>
       <c r="AG3" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AH3" t="str">
         <v/>
@@ -7908,13 +8087,13 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>Sydney Trains</v>
+        <v>Metropolitan Rail Operator</v>
       </c>
       <c r="AA4" t="str">
         <v>Both Directions</v>
       </c>
       <c r="AB4" t="str">
-        <v>Sydney Trains</v>
+        <v>Metropolitan Rail Operator</v>
       </c>
       <c r="AC4" t="str">
         <v/>
@@ -7929,7 +8108,7 @@
         <v/>
       </c>
       <c r="AG4" t="str">
-        <v>Sydney Trains</v>
+        <v>Metropolitan Rail Operator</v>
       </c>
       <c r="AH4" t="str">
         <v/>
@@ -8075,13 +8254,13 @@
         <v/>
       </c>
       <c r="Z5" t="str">
-        <v>TfNSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AA5" t="str">
         <v>Both Directions</v>
       </c>
       <c r="AB5" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AC5" t="str">
         <v/>
@@ -8096,7 +8275,7 @@
         <v/>
       </c>
       <c r="AG5" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AH5" t="str">
         <v/>
@@ -8242,13 +8421,13 @@
         <v/>
       </c>
       <c r="Z6" t="str">
-        <v>TfNSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AA6" t="str">
         <v>Both Directions</v>
       </c>
       <c r="AB6" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AC6" t="str">
         <v/>
@@ -8263,7 +8442,7 @@
         <v/>
       </c>
       <c r="AG6" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AH6" t="str">
         <v/>
@@ -8409,13 +8588,13 @@
         <v/>
       </c>
       <c r="Z7" t="str">
-        <v>TfNSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AA7" t="str">
         <v>Both Directions</v>
       </c>
       <c r="AB7" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AC7" t="str">
         <v/>
@@ -8430,7 +8609,7 @@
         <v/>
       </c>
       <c r="AG7" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AH7" t="str">
         <v/>
@@ -8576,13 +8755,13 @@
         <v/>
       </c>
       <c r="Z8" t="str">
-        <v>TfNSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AA8" t="str">
         <v>Both Directions</v>
       </c>
       <c r="AB8" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AC8" t="str">
         <v/>
@@ -8597,7 +8776,7 @@
         <v/>
       </c>
       <c r="AG8" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AH8" t="str">
         <v/>
@@ -9912,13 +10091,13 @@
         <v>2026-06-30</v>
       </c>
       <c r="Z16" t="str">
-        <v>TfNSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AA16" t="str">
         <v>Both Directions</v>
       </c>
       <c r="AB16" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AC16" t="str">
         <v>2026-02-01</v>
@@ -9933,7 +10112,7 @@
         <v>APR-NSW-2026-02</v>
       </c>
       <c r="AG16" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AH16" t="str">
         <v>NSW Gazette 2026/05</v>
@@ -10085,7 +10264,7 @@
         <v>Both Directions</v>
       </c>
       <c r="AB17" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AC17" t="str">
         <v/>
@@ -10100,7 +10279,7 @@
         <v>APR-NSW-2025-31</v>
       </c>
       <c r="AG17" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AH17" t="str">
         <v>NSW Gazette 2025/44</v>
@@ -10246,13 +10425,13 @@
         <v/>
       </c>
       <c r="Z18" t="str">
-        <v>TfNSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AA18" t="str">
         <v>Both Directions</v>
       </c>
       <c r="AB18" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AC18" t="str">
         <v/>
@@ -10267,7 +10446,7 @@
         <v/>
       </c>
       <c r="AG18" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AH18" t="str">
         <v/>
@@ -10580,13 +10759,13 @@
         <v/>
       </c>
       <c r="Z20" t="str">
-        <v>TfNSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AA20" t="str">
         <v>Both Directions</v>
       </c>
       <c r="AB20" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AC20" t="str">
         <v/>
@@ -10601,7 +10780,7 @@
         <v/>
       </c>
       <c r="AG20" t="str">
-        <v>Transport for NSW</v>
+        <v>State Roads Authority</v>
       </c>
       <c r="AH20" t="str">
         <v/>
@@ -10925,10 +11104,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Sydney Metro</v>
+        <v>Sydney Metropolitan</v>
       </c>
       <c r="B7" t="str">
-        <v>Sydney Metro</v>
+        <v>Sydney Metropolitan</v>
       </c>
       <c r="C7" t="str">
         <v/>
